--- a/out/M01_mobile_network_experience/agent3/agent3_test_cases_with_paths.xlsx
+++ b/out/M01_mobile_network_experience/agent3/agent3_test_cases_with_paths.xlsx
@@ -861,12 +861,12 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14  -&gt;  TERM_QUOTA_FULL</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14  -&gt;  TERM_QUOTA_FULL</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>11 test(s): TC-FT47, TC-FT48, TC-FT49, TC-FT50, TC-FT51, TC-FT52 ...</t>
+          <t>11 test(s): TC-FT45, TC-FT46, TC-FT47, TC-FT48, TC-FT49, TC-FT50 ...</t>
         </is>
       </c>
       <c r="Q7" s="8" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14  -&gt;  COMPLETE</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14  -&gt;  COMPLETE</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>52 test(s): TC-FT05, TC-FT06, TC-FT07, TC-FT08, TC-FT09, TC-FT10 ...</t>
+          <t>51 test(s): TC-FT05, TC-FT06, TC-FT07, TC-FT08, TC-FT09, TC-FT10 ...</t>
         </is>
       </c>
       <c r="Q8" s="8" t="inlineStr">
@@ -1045,12 +1045,12 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14  -&gt;  COMPLETE</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14  -&gt;  COMPLETE</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1137,12 +1137,12 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14  -&gt;  COMPLETE</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14  -&gt;  COMPLETE</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>14 test(s): TC-FT33, TC-FT34, TC-FT35, TC-FT36, TC-FT37, TC-FT38 ...</t>
+          <t>14 test(s): TC-FT31, TC-FT32, TC-FT33, TC-FT34, TC-FT35, TC-FT36 ...</t>
         </is>
       </c>
       <c r="Q10" s="8" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE87"/>
+  <dimension ref="A1:AE86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T5" s="6" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="U6" s="6" t="inlineStr">
         <is>
-          <t>S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V6" s="6" t="inlineStr">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T8" s="6" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="U9" s="6" t="inlineStr">
         <is>
-          <t>S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S11" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T11" s="6" t="inlineStr">
@@ -2475,7 +2475,7 @@
       <c r="W11" s="6" t="inlineStr">
         <is>
           <t>1. S3 is on screen
-2. the next question shown is Q1</t>
+2. the next question shown is DT1</t>
         </is>
       </c>
       <c r="X11" s="6" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S12" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="U13" s="6" t="inlineStr">
         <is>
-          <t>Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V13" s="6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>DT1</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Q1 accepts a normal answer and the survey moves on</t>
+          <t>DT1 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q1 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove that answering DT1 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q1.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as DT1.</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q1 is the one the claim turns on.</t>
+          <t>Every answer before DT1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at DT1 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -2944,8 +2944,7 @@
       </c>
       <c r="W14" s="6" t="inlineStr">
         <is>
-          <t>1. Q1 is on screen
-2. the next question shown is Q2</t>
+          <t>1. the next question shown is Q1</t>
         </is>
       </c>
       <c r="X14" s="6" t="inlineStr">
@@ -2960,7 +2959,7 @@
       </c>
       <c r="Z14" s="6" t="inlineStr">
         <is>
-          <t>Q1 | Which mobile network services channel or provider did you use most recently? | single | Provider A; Provider B; Provider C; Provider D | Always show</t>
+          <t>DT1 | Great, you're eligible for this survey! Next, a few questions about your recent mobile network experience. | text display | — | Always show</t>
         </is>
       </c>
       <c r="AA14" s="6" t="inlineStr">
@@ -3010,12 +3009,12 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -3025,22 +3024,22 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Q1 blocks a blank answer</t>
+          <t>Q1 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>Prove Q1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove that answering Q1 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -3055,13 +3054,13 @@
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18
-then: At Q1, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
@@ -3071,17 +3070,17 @@
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>At Q1, select nothing at all, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1  (refused at Q1; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -3091,23 +3090,23 @@
       </c>
       <c r="U15" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W15" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q1</t>
+          <t>1. Q1 is on screen
+2. the next question shown is Q2</t>
         </is>
       </c>
       <c r="X15" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y15" s="6" t="inlineStr">
@@ -3125,9 +3124,9 @@
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB15" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
+      <c r="AB15" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
         </is>
       </c>
       <c r="AC15" s="8" t="inlineStr">
@@ -3137,12 +3136,12 @@
       </c>
       <c r="AD15" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE15" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3151,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -3167,139 +3166,139 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
+          <t>10. Negative / Robustness</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Q1 blocks a blank answer</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Prove Q1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q1.</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; S3 = 18
+then: At Q1, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q1 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>At Q1, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1  (refused at Q1; respondent stays put)</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, S3, DT1, Q1</t>
+        </is>
+      </c>
+      <c r="T16" s="6" t="inlineStr">
+        <is>
+          <t>Q8, Q9, Q10</t>
+        </is>
+      </c>
+      <c r="U16" s="6" t="inlineStr">
+        <is>
+          <t>Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+        </is>
+      </c>
+      <c r="V16" s="6" t="inlineStr">
+        <is>
+          <t>No forward navigation - the same question must reappear.</t>
+        </is>
+      </c>
+      <c r="W16" s="6" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q1</t>
+        </is>
+      </c>
+      <c r="X16" s="6" t="inlineStr">
+        <is>
+          <t>Not reached - the respondent cannot progress</t>
+        </is>
+      </c>
+      <c r="Y16" s="6" t="inlineStr">
+        <is>
+          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
+        </is>
+      </c>
+      <c r="Z16" s="6" t="inlineStr">
+        <is>
+          <t>Q1 | Which mobile network services channel or provider did you use most recently? | single | Provider A; Provider B; Provider C; Provider D | Always show</t>
+        </is>
+      </c>
+      <c r="AA16" s="6" t="inlineStr">
+        <is>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
+        </is>
+      </c>
+      <c r="AB16" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="AC16" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AD16" s="6" t="inlineStr">
+        <is>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+        </is>
+      </c>
+      <c r="AE16" s="6" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Q2 accepts a normal answer and the survey moves on</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>Prove that answering Q2 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
-        </is>
-      </c>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q2.</t>
-        </is>
-      </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N16" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
-        </is>
-      </c>
-      <c r="O16" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q2 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
-        </is>
-      </c>
-      <c r="S16" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
-        </is>
-      </c>
-      <c r="T16" s="6" t="inlineStr">
-        <is>
-          <t>Q8, Q9, Q10</t>
-        </is>
-      </c>
-      <c r="U16" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V16" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W16" s="6" t="inlineStr">
-        <is>
-          <t>1. Q2 is on screen
-2. the next question shown is Q3</t>
-        </is>
-      </c>
-      <c r="X16" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y16" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z16" s="6" t="inlineStr">
-        <is>
-          <t>Q2 | When did the most recent experience occur? | single | Within 7 days; 8-30 days; 1-3 months; 4-6 months | Always show</t>
-        </is>
-      </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB16" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC16" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD16" s="6" t="inlineStr">
-        <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
-        </is>
-      </c>
-      <c r="AE16" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
       </c>
     </row>
@@ -3324,12 +3323,12 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -3339,22 +3338,22 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Q2 blocks a blank answer</t>
+          <t>Q2 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>Prove Q2 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove that answering Q2 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -3369,13 +3368,13 @@
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A
-then: At Q2, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
@@ -3385,17 +3384,17 @@
       </c>
       <c r="Q17" s="6" t="inlineStr">
         <is>
-          <t>At Q2, select nothing at all, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2  (refused at Q2; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S17" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -3405,23 +3404,23 @@
       </c>
       <c r="U17" s="6" t="inlineStr">
         <is>
-          <t>Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W17" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q2</t>
+          <t>1. Q2 is on screen
+2. the next question shown is Q3</t>
         </is>
       </c>
       <c r="X17" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y17" s="6" t="inlineStr">
@@ -3439,9 +3438,9 @@
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB17" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
+      <c r="AB17" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
         </is>
       </c>
       <c r="AC17" s="8" t="inlineStr">
@@ -3451,12 +3450,12 @@
       </c>
       <c r="AD17" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE17" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
       </c>
     </row>
@@ -3481,138 +3480,139 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
+          <t>10. Negative / Robustness</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Q2 blocks a blank answer</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Prove Q2 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q2.</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A
+then: At Q2, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="O18" s="6" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q2 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>At Q2, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2  (refused at Q2; respondent stays put)</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, S3, DT1, Q1, Q2</t>
+        </is>
+      </c>
+      <c r="T18" s="6" t="inlineStr">
+        <is>
+          <t>Q8, Q9, Q10</t>
+        </is>
+      </c>
+      <c r="U18" s="6" t="inlineStr">
+        <is>
+          <t>Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+        </is>
+      </c>
+      <c r="V18" s="6" t="inlineStr">
+        <is>
+          <t>No forward navigation - the same question must reappear.</t>
+        </is>
+      </c>
+      <c r="W18" s="6" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q2</t>
+        </is>
+      </c>
+      <c r="X18" s="6" t="inlineStr">
+        <is>
+          <t>Not reached - the respondent cannot progress</t>
+        </is>
+      </c>
+      <c r="Y18" s="6" t="inlineStr">
+        <is>
+          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
+        </is>
+      </c>
+      <c r="Z18" s="6" t="inlineStr">
+        <is>
+          <t>Q2 | When did the most recent experience occur? | single | Within 7 days; 8-30 days; 1-3 months; 4-6 months | Always show</t>
+        </is>
+      </c>
+      <c r="AA18" s="6" t="inlineStr">
+        <is>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
+        </is>
+      </c>
+      <c r="AB18" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="AC18" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AD18" s="6" t="inlineStr">
+        <is>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+        </is>
+      </c>
+      <c r="AE18" s="6" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Q2 quotes the answer given at Q1</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q2's wording is built from the answer given at Q1, so the respondent is only asked about what they actually chose.</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
-        </is>
-      </c>
-      <c r="K18" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q2.</t>
-        </is>
-      </c>
-      <c r="M18" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N18" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A
-then: At Q2, choose “Within 7 days”, then submit.</t>
-        </is>
-      </c>
-      <c r="O18" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q2 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>At Q2, choose “Within 7 days”, then submit.</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
-        </is>
-      </c>
-      <c r="S18" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
-        </is>
-      </c>
-      <c r="T18" s="6" t="inlineStr">
-        <is>
-          <t>Q8, Q9, Q10</t>
-        </is>
-      </c>
-      <c r="U18" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V18" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W18" s="6" t="inlineStr">
-        <is>
-          <t>1. Q2's wording includes: Provider A</t>
-        </is>
-      </c>
-      <c r="X18" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y18" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z18" s="6" t="inlineStr">
-        <is>
-          <t>Q2 | When did the most recent experience occur? | single | Within 7 days; 8-30 days; 1-3 months; 4-6 months | Always show</t>
-        </is>
-      </c>
-      <c r="AA18" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB18" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC18" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD18" s="6" t="inlineStr">
-        <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
-        </is>
-      </c>
-      <c r="AE18" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
       </c>
     </row>
@@ -3703,12 +3703,12 @@
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S19" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3  (refused at Q3; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3  (refused at Q3; respondent stays put)</t>
         </is>
       </c>
       <c r="S20" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="U20" s="6" t="inlineStr">
         <is>
-          <t>Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V20" s="6" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>4. Randomization</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8. Implementation Conformance</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
@@ -3966,17 +3966,17 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Q3 quotes the answer given at Q1</t>
+          <t>Q3 shuffles without losing an option</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>Prove Q3's wording is built from the answer given at Q1, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove Q3 still presents all 5 of its options when shuffled, with none dropped and none repeated.</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
+          <t>Without a genuine shuffle the option order biases the answers, and without the recorded order the answers cannot be corrected later.</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
@@ -4017,12 +4017,12 @@
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S21" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T21" s="6" t="inlineStr">
@@ -4042,7 +4042,8 @@
       </c>
       <c r="W21" s="6" t="inlineStr">
         <is>
-          <t>1. Q3's wording includes: Provider A</t>
+          <t>1. Q3 shows exactly 5 options, none missing or repeated
+2. the options shown at Q3 are exactly: Calls, Customer support, International roaming, Mobile data, Recharge or billing</t>
         </is>
       </c>
       <c r="X21" s="6" t="inlineStr">
@@ -4077,7 +4078,7 @@
       </c>
       <c r="AD21" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the order varies, only that nothing was lost or repeated. Order is a separate test needing several runs.</t>
         </is>
       </c>
       <c r="AE21" s="6" t="inlineStr">
@@ -4097,12 +4098,12 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>TC-FT16</t>
+          <t>TC-ST01</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>FOCUSED</t>
+          <t>STATEFUL</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -4122,12 +4123,12 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Q3 shuffles without losing an option</t>
+          <t>Q3 genuinely varies its option order</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>Prove Q3 still presents all 5 of its options when shuffled, with none dropped and none repeated.</t>
+          <t>Prove Q3 is genuinely shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on.</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
@@ -4142,7 +4143,7 @@
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q3.</t>
+          <t>Run this same path 5 times and compare the recorded option order between runs.</t>
         </is>
       </c>
       <c r="M22" s="6" t="inlineStr">
@@ -4173,12 +4174,12 @@
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S22" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -4198,8 +4199,7 @@
       </c>
       <c r="W22" s="6" t="inlineStr">
         <is>
-          <t>1. Q3 shows exactly 5 options, none missing or repeated
-2. the options shown at Q3 are exactly: Calls, Customer support, International roaming, Mobile data, Recharge or billing</t>
+          <t>1. the option order at Q3 is NOT identical on every run</t>
         </is>
       </c>
       <c r="X22" s="6" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AD22" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the order varies, only that nothing was lost or repeated. Order is a separate test needing several runs.</t>
+          <t>It does not prove any particular order is correct, only that the order is not fixed.</t>
         </is>
       </c>
       <c r="AE22" s="6" t="inlineStr">
@@ -4249,27 +4249,27 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>TC-ST01</t>
+          <t>TC-FT16</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>STATEFUL</t>
+          <t>FOCUSED</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>4. Randomization</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>8. Implementation Conformance</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -4279,27 +4279,27 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Q3 genuinely varies its option order</t>
+          <t>Q4 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>Prove Q3 is genuinely shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on.</t>
+          <t>Prove that answering Q4 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>Without a genuine shuffle the option order biases the answers, and without the recorded order the answers cannot be corrected later.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>Run this same path 5 times and compare the recorded option order between runs.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q4.</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
@@ -4309,8 +4309,8 @@
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days
-then: At Q3, choose “Calls”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr">
@@ -4320,22 +4320,22 @@
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q3 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q3 is the one the claim turns on.</t>
+          <t>Every answer before Q4 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q4 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>At Q3, choose “Calls”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S23" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T23" s="6" t="inlineStr">
@@ -4355,7 +4355,8 @@
       </c>
       <c r="W23" s="6" t="inlineStr">
         <is>
-          <t>1. the option order at Q3 is NOT identical on every run</t>
+          <t>1. Q4 is on screen
+2. the next question shown is Q5</t>
         </is>
       </c>
       <c r="X23" s="6" t="inlineStr">
@@ -4370,7 +4371,7 @@
       </c>
       <c r="Z23" s="6" t="inlineStr">
         <is>
-          <t>Q3 | What was the primary purpose of the experience? | single | Calls; Mobile data; Recharge or billing; Customer support; International roaming | Randomize</t>
+          <t>Q4 | Rate your overall satisfaction. | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
       <c r="AA23" s="6" t="inlineStr">
@@ -4390,7 +4391,7 @@
       </c>
       <c r="AD23" s="6" t="inlineStr">
         <is>
-          <t>It does not prove any particular order is correct, only that the order is not fixed.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE23" s="6" t="inlineStr">
@@ -4420,139 +4421,139 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
+          <t>10. Negative / Robustness</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Q4 blocks a blank answer</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Prove Q4 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q4.</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls
+then: At Q4, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q4 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q4 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>At Q4, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4  (refused at Q4; respondent stays put)</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4</t>
+        </is>
+      </c>
+      <c r="T24" s="6" t="inlineStr">
+        <is>
+          <t>Q8, Q9, Q10</t>
+        </is>
+      </c>
+      <c r="U24" s="6" t="inlineStr">
+        <is>
+          <t>Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+        </is>
+      </c>
+      <c r="V24" s="6" t="inlineStr">
+        <is>
+          <t>No forward navigation - the same question must reappear.</t>
+        </is>
+      </c>
+      <c r="W24" s="6" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q4</t>
+        </is>
+      </c>
+      <c r="X24" s="6" t="inlineStr">
+        <is>
+          <t>Not reached - the respondent cannot progress</t>
+        </is>
+      </c>
+      <c r="Y24" s="6" t="inlineStr">
+        <is>
+          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
+        </is>
+      </c>
+      <c r="Z24" s="6" t="inlineStr">
+        <is>
+          <t>Q4 | Rate your overall satisfaction. | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
+        </is>
+      </c>
+      <c r="AA24" s="6" t="inlineStr">
+        <is>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
+        </is>
+      </c>
+      <c r="AB24" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="AC24" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AD24" s="6" t="inlineStr">
+        <is>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+        </is>
+      </c>
+      <c r="AE24" s="6" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Q4 accepts a normal answer and the survey moves on</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>Prove that answering Q4 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
-        </is>
-      </c>
-      <c r="J24" s="6" t="inlineStr">
-        <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
-        </is>
-      </c>
-      <c r="K24" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L24" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q4.</t>
-        </is>
-      </c>
-      <c r="M24" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N24" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
-        </is>
-      </c>
-      <c r="O24" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q4 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q4 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
-        </is>
-      </c>
-      <c r="S24" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
-        </is>
-      </c>
-      <c r="T24" s="6" t="inlineStr">
-        <is>
-          <t>Q8, Q9, Q10</t>
-        </is>
-      </c>
-      <c r="U24" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V24" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W24" s="6" t="inlineStr">
-        <is>
-          <t>1. Q4 is on screen
-2. the next question shown is Q5</t>
-        </is>
-      </c>
-      <c r="X24" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y24" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z24" s="6" t="inlineStr">
-        <is>
-          <t>Q4 | Rate your overall satisfaction. | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
-        </is>
-      </c>
-      <c r="AA24" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB24" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC24" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD24" s="6" t="inlineStr">
-        <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
-        </is>
-      </c>
-      <c r="AE24" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
       </c>
     </row>
@@ -4562,7 +4563,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -4577,12 +4578,12 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -4592,27 +4593,27 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Q4 blocks a blank answer</t>
+          <t>Q5 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>Prove Q4 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove that answering Q5 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q4.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q5.</t>
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr">
@@ -4622,33 +4623,33 @@
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls
-then: At Q4, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O25" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q4 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q4 is the one the claim turns on.</t>
+          <t>Every answer before Q5 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q5 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>At Q4, select nothing at all, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4  (refused at Q4; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S25" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T25" s="6" t="inlineStr">
@@ -4658,23 +4659,23 @@
       </c>
       <c r="U25" s="6" t="inlineStr">
         <is>
-          <t>Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V25" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W25" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q4</t>
+          <t>1. Q5 is on screen
+2. the next question shown is Q6</t>
         </is>
       </c>
       <c r="X25" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y25" s="6" t="inlineStr">
@@ -4684,7 +4685,7 @@
       </c>
       <c r="Z25" s="6" t="inlineStr">
         <is>
-          <t>Q4 | Rate your overall satisfaction. | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
+          <t>Q5 | Rate the ease of completing the experience. | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
       <c r="AA25" s="6" t="inlineStr">
@@ -4692,9 +4693,9 @@
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB25" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
+      <c r="AB25" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
         </is>
       </c>
       <c r="AC25" s="8" t="inlineStr">
@@ -4704,12 +4705,12 @@
       </c>
       <c r="AD25" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE25" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
       </c>
     </row>
@@ -4734,139 +4735,139 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
+          <t>10. Negative / Robustness</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Q5 blocks a blank answer</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>Prove Q5 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q5.</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor
+then: At Q5, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q5 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q5 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>At Q5, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5  (refused at Q5; respondent stays put)</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5</t>
+        </is>
+      </c>
+      <c r="T26" s="6" t="inlineStr">
+        <is>
+          <t>Q8, Q9, Q10</t>
+        </is>
+      </c>
+      <c r="U26" s="6" t="inlineStr">
+        <is>
+          <t>Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+        </is>
+      </c>
+      <c r="V26" s="6" t="inlineStr">
+        <is>
+          <t>No forward navigation - the same question must reappear.</t>
+        </is>
+      </c>
+      <c r="W26" s="6" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q5</t>
+        </is>
+      </c>
+      <c r="X26" s="6" t="inlineStr">
+        <is>
+          <t>Not reached - the respondent cannot progress</t>
+        </is>
+      </c>
+      <c r="Y26" s="6" t="inlineStr">
+        <is>
+          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
+        </is>
+      </c>
+      <c r="Z26" s="6" t="inlineStr">
+        <is>
+          <t>Q5 | Rate the ease of completing the experience. | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
+        </is>
+      </c>
+      <c r="AA26" s="6" t="inlineStr">
+        <is>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
+        </is>
+      </c>
+      <c r="AB26" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="AC26" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AD26" s="6" t="inlineStr">
+        <is>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+        </is>
+      </c>
+      <c r="AE26" s="6" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>Q5 accepts a normal answer and the survey moves on</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>Prove that answering Q5 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
-        <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
-        </is>
-      </c>
-      <c r="K26" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L26" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q5.</t>
-        </is>
-      </c>
-      <c r="M26" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N26" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
-        </is>
-      </c>
-      <c r="O26" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q5 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q5 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
-        </is>
-      </c>
-      <c r="S26" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
-        </is>
-      </c>
-      <c r="T26" s="6" t="inlineStr">
-        <is>
-          <t>Q8, Q9, Q10</t>
-        </is>
-      </c>
-      <c r="U26" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V26" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W26" s="6" t="inlineStr">
-        <is>
-          <t>1. Q5 is on screen
-2. the next question shown is Q6</t>
-        </is>
-      </c>
-      <c r="X26" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y26" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z26" s="6" t="inlineStr">
-        <is>
-          <t>Q5 | Rate the ease of completing the experience. | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
-        </is>
-      </c>
-      <c r="AA26" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB26" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC26" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD26" s="6" t="inlineStr">
-        <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
-        </is>
-      </c>
-      <c r="AE26" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4877,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -4891,12 +4892,12 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
@@ -4906,27 +4907,27 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Q5 blocks a blank answer</t>
+          <t>Q6 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>Prove Q5 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove that answering Q6 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q5.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q6.</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
@@ -4936,33 +4937,33 @@
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor
-then: At Q5, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q5 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q5 is the one the claim turns on.</t>
+          <t>Every answer before Q6 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q6 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>At Q5, select nothing at all, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5  (refused at Q5; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S27" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T27" s="6" t="inlineStr">
@@ -4972,23 +4973,23 @@
       </c>
       <c r="U27" s="6" t="inlineStr">
         <is>
-          <t>Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V27" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W27" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q5</t>
+          <t>1. Q6 is on screen
+2. the next question shown is Q7_SQ001</t>
         </is>
       </c>
       <c r="X27" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y27" s="6" t="inlineStr">
@@ -4998,7 +4999,7 @@
       </c>
       <c r="Z27" s="6" t="inlineStr">
         <is>
-          <t>Q5 | Rate the ease of completing the experience. | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
+          <t>Q6 | Rate the clarity of information provided. | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
       <c r="AA27" s="6" t="inlineStr">
@@ -5006,9 +5007,9 @@
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB27" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
+      <c r="AB27" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
         </is>
       </c>
       <c r="AC27" s="8" t="inlineStr">
@@ -5018,12 +5019,12 @@
       </c>
       <c r="AD27" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE27" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5034,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -5048,138 +5049,139 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
+          <t>10. Negative / Robustness</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Q6 blocks a blank answer</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Prove Q6 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q6.</t>
+        </is>
+      </c>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor
+then: At Q6, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="O28" s="6" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q6 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q6 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>At Q6, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6</t>
+        </is>
+      </c>
+      <c r="T28" s="6" t="inlineStr">
+        <is>
+          <t>Q8, Q9, Q10</t>
+        </is>
+      </c>
+      <c r="U28" s="6" t="inlineStr">
+        <is>
+          <t>Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+        </is>
+      </c>
+      <c r="V28" s="6" t="inlineStr">
+        <is>
+          <t>No forward navigation - the same question must reappear.</t>
+        </is>
+      </c>
+      <c r="W28" s="6" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q6</t>
+        </is>
+      </c>
+      <c r="X28" s="6" t="inlineStr">
+        <is>
+          <t>Not reached - the respondent cannot progress</t>
+        </is>
+      </c>
+      <c r="Y28" s="6" t="inlineStr">
+        <is>
+          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
+        </is>
+      </c>
+      <c r="Z28" s="6" t="inlineStr">
+        <is>
+          <t>Q6 | Rate the clarity of information provided. | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
+        </is>
+      </c>
+      <c r="AA28" s="6" t="inlineStr">
+        <is>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
+        </is>
+      </c>
+      <c r="AB28" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="AC28" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AD28" s="6" t="inlineStr">
+        <is>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+        </is>
+      </c>
+      <c r="AE28" s="6" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>Q5 quotes the answer given at Q1</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q5's wording is built from the answer given at Q1, so the respondent is only asked about what they actually chose.</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="inlineStr">
-        <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
-        </is>
-      </c>
-      <c r="K28" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L28" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q5.</t>
-        </is>
-      </c>
-      <c r="M28" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N28" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor
-then: At Q5, choose “Very poor”, then submit.</t>
-        </is>
-      </c>
-      <c r="O28" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q5 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q5 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>At Q5, choose “Very poor”, then submit.</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
-        </is>
-      </c>
-      <c r="S28" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
-        </is>
-      </c>
-      <c r="T28" s="6" t="inlineStr">
-        <is>
-          <t>Q8, Q9, Q10</t>
-        </is>
-      </c>
-      <c r="U28" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V28" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W28" s="6" t="inlineStr">
-        <is>
-          <t>1. Q5's wording includes: Provider A</t>
-        </is>
-      </c>
-      <c r="X28" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y28" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z28" s="6" t="inlineStr">
-        <is>
-          <t>Q5 | Rate the ease of completing the experience. | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
-        </is>
-      </c>
-      <c r="AA28" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB28" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC28" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD28" s="6" t="inlineStr">
-        <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
-        </is>
-      </c>
-      <c r="AE28" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5191,7 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -5219,12 +5221,12 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Q6 accepts a normal answer and the survey moves on</t>
+          <t>Q7 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q6 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove that answering Q7 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
@@ -5239,7 +5241,7 @@
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q6.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q7.</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
@@ -5260,7 +5262,7 @@
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q6 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q6 is the one the claim turns on.</t>
+          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
@@ -5270,12 +5272,12 @@
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S29" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T29" s="6" t="inlineStr">
@@ -5295,8 +5297,8 @@
       </c>
       <c r="W29" s="6" t="inlineStr">
         <is>
-          <t>1. Q6 is on screen
-2. the next question shown is Q7_SQ001</t>
+          <t>1. Q7 is on screen
+2. the next question shown is Q8</t>
         </is>
       </c>
       <c r="X29" s="6" t="inlineStr">
@@ -5311,7 +5313,8 @@
       </c>
       <c r="Z29" s="6" t="inlineStr">
         <is>
-          <t>Q6 | Rate the clarity of information provided. | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
+          <t>Q7 | Did you experience any of the following problems? | multi | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay; None of these | Validate: {"exclusive_option": "None of these"}
+Randomize</t>
         </is>
       </c>
       <c r="AA29" s="6" t="inlineStr">
@@ -5346,7 +5349,7 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -5361,12 +5364,12 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
@@ -5376,27 +5379,27 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Q6 blocks a blank answer</t>
+          <t>R6 jumps forward when its condition is met</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove R6 jumps to Q11. The rule is: Q7 == ['None of these']</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q6.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q7.</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
@@ -5406,33 +5409,33 @@
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor
-then: At Q6, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor
+then: At Q7, tick 1 option (None of these), then submit.</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q6 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q6 is the one the claim turns on.</t>
+          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>At Q6, select nothing at all, then submit.</t>
+          <t>At Q7, tick 1 option (None of these), then submit.</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S30" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T30" s="6" t="inlineStr">
@@ -5442,23 +5445,22 @@
       </c>
       <c r="U30" s="6" t="inlineStr">
         <is>
-          <t>Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>Q8, Q9, Q10</t>
         </is>
       </c>
       <c r="V30" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W30" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q6</t>
+          <t>1. the next question shown is Q11</t>
         </is>
       </c>
       <c r="X30" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y30" s="6" t="inlineStr">
@@ -5468,7 +5470,9 @@
       </c>
       <c r="Z30" s="6" t="inlineStr">
         <is>
-          <t>Q6 | Rate the clarity of information provided. | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
+          <t>Q7 | Did you experience any of the following problems? | multi | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay; None of these | Validate: {"exclusive_option": "None of these"}
+Randomize
+Rules exercised: R6</t>
         </is>
       </c>
       <c r="AA30" s="6" t="inlineStr">
@@ -5476,9 +5480,9 @@
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB30" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
+      <c r="AB30" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
         </is>
       </c>
       <c r="AC30" s="8" t="inlineStr">
@@ -5488,12 +5492,12 @@
       </c>
       <c r="AD30" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE30" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Leans on an unconfirmed reading: multi_equality, rule_precedence</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5527,7 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
@@ -5533,12 +5537,12 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Q7 accepts a normal answer and the survey moves on</t>
+          <t>R6 does not jump when its condition is not met</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q7 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove R6 does not jump and the respondent continues in sequence. The rule is: Q7 == ['None of these']</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
@@ -5563,8 +5567,8 @@
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor
+then: At Q7, tick 1 option (Dropped calls), then submit.</t>
         </is>
       </c>
       <c r="O31" s="6" t="inlineStr">
@@ -5579,17 +5583,17 @@
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q7, tick 1 option (Dropped calls), then submit.</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S31" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T31" s="6" t="inlineStr">
@@ -5609,8 +5613,7 @@
       </c>
       <c r="W31" s="6" t="inlineStr">
         <is>
-          <t>1. Q7 is on screen
-2. the next question shown is Q8</t>
+          <t>1. the next question shown is Q8</t>
         </is>
       </c>
       <c r="X31" s="6" t="inlineStr">
@@ -5626,7 +5629,8 @@
       <c r="Z31" s="6" t="inlineStr">
         <is>
           <t>Q7 | Did you experience any of the following problems? | multi | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay; None of these | Validate: {"exclusive_option": "None of these"}
-Randomize</t>
+Randomize
+Rules exercised: R6</t>
         </is>
       </c>
       <c r="AA31" s="6" t="inlineStr">
@@ -5646,7 +5650,7 @@
       </c>
       <c r="AD31" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE31" s="6" t="inlineStr">
@@ -5676,7 +5680,7 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -5691,17 +5695,17 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>R6 jumps forward when its condition is met</t>
+          <t>Q7 accepts a valid answer</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>Prove R6 jumps to Q11. The rule is: Q7 == ['None of these']</t>
+          <t>Prove Q7 accepts an answer that obeys its stated rule. The rule is: “None of these” cannot be chosen alongside anything else</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
@@ -5727,7 +5731,7 @@
       </c>
       <c r="O32" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>VALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P32" s="6" t="inlineStr">
@@ -5742,12 +5746,12 @@
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S32" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T32" s="6" t="inlineStr">
@@ -5767,7 +5771,7 @@
       </c>
       <c r="W32" s="6" t="inlineStr">
         <is>
-          <t>1. the next question shown is Q11</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X32" s="6" t="inlineStr">
@@ -5783,8 +5787,7 @@
       <c r="Z32" s="6" t="inlineStr">
         <is>
           <t>Q7 | Did you experience any of the following problems? | multi | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay; None of these | Validate: {"exclusive_option": "None of these"}
-Randomize
-Rules exercised: R6</t>
+Randomize</t>
         </is>
       </c>
       <c r="AA32" s="6" t="inlineStr">
@@ -5804,7 +5807,7 @@
       </c>
       <c r="AD32" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE32" s="6" t="inlineStr">
@@ -5834,12 +5837,12 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -5849,17 +5852,17 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>R6 does not jump when its condition is not met</t>
+          <t>Reject rule R9 does not fire</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>Prove R6 does not jump and the respondent continues in sequence. The rule is: Q7 == ['None of these']</t>
+          <t>Prove reject rule R9 does not fire when its condition is not met. The rule is: Q7 includes 'None of these' plus another option</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
@@ -5885,7 +5888,7 @@
       </c>
       <c r="O33" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>VALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P33" s="6" t="inlineStr">
@@ -5900,12 +5903,12 @@
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S33" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T33" s="6" t="inlineStr">
@@ -5925,7 +5928,7 @@
       </c>
       <c r="W33" s="6" t="inlineStr">
         <is>
-          <t>1. the next question shown is Q8</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X33" s="6" t="inlineStr">
@@ -5942,12 +5945,12 @@
         <is>
           <t>Q7 | Did you experience any of the following problems? | multi | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay; None of these | Validate: {"exclusive_option": "None of these"}
 Randomize
-Rules exercised: R6</t>
+Rules exercised: R9</t>
         </is>
       </c>
       <c r="AA33" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Model-inferred. The questionnaire wrote this as prose rather than in a table, so Agent 1 read it with a model and raised it for sign-off. Confirm before relying on this test.</t>
         </is>
       </c>
       <c r="AB33" s="10" t="inlineStr">
@@ -5962,7 +5965,7 @@
       </c>
       <c r="AD33" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE33" s="6" t="inlineStr">
@@ -5997,7 +6000,7 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -6007,12 +6010,12 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Q7 accepts a valid answer</t>
+          <t>Q7 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>Prove Q7 accepts an answer that obeys its stated rule. The rule is: “None of these” cannot be chosen alongside anything else</t>
+          <t>Prove Q7 refuses an answer that breaks its stated rule. The rule is: “None of these” cannot be chosen alongside anything else</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
@@ -6038,12 +6041,12 @@
       <c r="N34" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor
-then: At Q7, tick 1 option (None of these), then submit.</t>
+then: At Q7, tick 2 options (None of these, Dropped calls), then submit.</t>
         </is>
       </c>
       <c r="O34" s="6" t="inlineStr">
         <is>
-          <t>VALID_BOUNDARY</t>
+          <t>INVALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P34" s="6" t="inlineStr">
@@ -6053,17 +6056,17 @@
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>At Q7, tick 1 option (None of these), then submit.</t>
+          <t>At Q7, tick 2 options (None of these, Dropped calls), then submit.</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7  (refused at Q7; respondent stays put)</t>
         </is>
       </c>
       <c r="S34" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7</t>
         </is>
       </c>
       <c r="T34" s="6" t="inlineStr">
@@ -6073,22 +6076,23 @@
       </c>
       <c r="U34" s="6" t="inlineStr">
         <is>
-          <t>Q8, Q9, Q10</t>
+          <t>Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V34" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W34" s="6" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q7</t>
         </is>
       </c>
       <c r="X34" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y34" s="6" t="inlineStr">
@@ -6107,9 +6111,9 @@
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB34" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
+      <c r="AB34" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="AC34" s="8" t="inlineStr">
@@ -6124,7 +6128,7 @@
       </c>
       <c r="AE34" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality, rule_precedence</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6158,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -6164,12 +6168,12 @@
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Reject rule R9 does not fire</t>
+          <t>Reject rule R9 fires</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>Prove reject rule R9 does not fire when its condition is not met. The rule is: Q7 includes 'None of these' plus another option</t>
+          <t>Prove reject rule R9 fires when its condition is met. The rule is: Q7 includes 'None of these' plus another option</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
@@ -6195,12 +6199,12 @@
       <c r="N35" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor
-then: At Q7, tick 1 option (Dropped calls), then submit.</t>
+then: At Q7, tick 2 options (Dropped calls, None of these), then submit.</t>
         </is>
       </c>
       <c r="O35" s="6" t="inlineStr">
         <is>
-          <t>VALID_BOUNDARY</t>
+          <t>INVALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P35" s="6" t="inlineStr">
@@ -6210,17 +6214,17 @@
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
-          <t>At Q7, tick 1 option (Dropped calls), then submit.</t>
+          <t>At Q7, tick 2 options (Dropped calls, None of these), then submit.</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7  (refused at Q7; respondent stays put)</t>
         </is>
       </c>
       <c r="S35" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7</t>
         </is>
       </c>
       <c r="T35" s="6" t="inlineStr">
@@ -6230,22 +6234,23 @@
       </c>
       <c r="U35" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V35" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W35" s="6" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against R9</t>
         </is>
       </c>
       <c r="X35" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y35" s="6" t="inlineStr">
@@ -6265,9 +6270,9 @@
           <t>Model-inferred. The questionnaire wrote this as prose rather than in a table, so Agent 1 read it with a model and raised it for sign-off. Confirm before relying on this test.</t>
         </is>
       </c>
-      <c r="AB35" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
+      <c r="AB35" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="AC35" s="8" t="inlineStr">
@@ -6282,7 +6287,7 @@
       </c>
       <c r="AE35" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6322,22 +6327,22 @@
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>Q7 rejects an invalid answer</t>
+          <t>Q7 blocks a blank answer</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>Prove Q7 refuses an answer that breaks its stated rule. The rule is: “None of these” cannot be chosen alongside anything else</t>
+          <t>Prove Q7 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a multi question.</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
@@ -6353,12 +6358,12 @@
       <c r="N36" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor
-then: At Q7, tick 2 options (None of these, Dropped calls), then submit.</t>
+then: At Q7, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O36" s="6" t="inlineStr">
         <is>
-          <t>INVALID_BOUNDARY</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P36" s="6" t="inlineStr">
@@ -6368,17 +6373,17 @@
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
-          <t>At Q7, tick 2 options (None of these, Dropped calls), then submit.</t>
+          <t>At Q7, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7  (refused at Q7; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7  (refused at Q7; respondent stays put)</t>
         </is>
       </c>
       <c r="S36" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7</t>
         </is>
       </c>
       <c r="T36" s="6" t="inlineStr">
@@ -6388,7 +6393,7 @@
       </c>
       <c r="U36" s="6" t="inlineStr">
         <is>
-          <t>Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V36" s="6" t="inlineStr">
@@ -6435,7 +6440,7 @@
       </c>
       <c r="AD36" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE36" s="6" t="inlineStr">
@@ -6465,12 +6470,12 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>4. Randomization</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>8. Implementation Conformance</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -6480,22 +6485,22 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Reject rule R9 fires</t>
+          <t>Q7 shuffles without losing an option</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>Prove reject rule R9 fires when its condition is met. The rule is: Q7 includes 'None of these' plus another option</t>
+          <t>Prove Q7 still presents all 6 of its options when shuffled, with none dropped and none repeated.</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>Without a genuine shuffle the option order biases the answers, and without the recorded order the answers cannot be corrected later.</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
@@ -6511,12 +6516,12 @@
       <c r="N37" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor
-then: At Q7, tick 2 options (Dropped calls, None of these), then submit.</t>
+then: At Q7, tick 1 option (Dropped calls), then submit.</t>
         </is>
       </c>
       <c r="O37" s="6" t="inlineStr">
         <is>
-          <t>INVALID_BOUNDARY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
@@ -6526,17 +6531,17 @@
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
-          <t>At Q7, tick 2 options (Dropped calls, None of these), then submit.</t>
+          <t>At Q7, tick 1 option (Dropped calls), then submit.</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7  (refused at Q7; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S37" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T37" s="6" t="inlineStr">
@@ -6546,23 +6551,23 @@
       </c>
       <c r="U37" s="6" t="inlineStr">
         <is>
-          <t>Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V37" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W37" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against R9</t>
+          <t>1. Q7 shows exactly 6 options, none missing or repeated
+2. the options shown at Q7 are exactly: Coverage gap, Dropped calls, None of these, Slow data, Support delay, Unexpected charge</t>
         </is>
       </c>
       <c r="X37" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y37" s="6" t="inlineStr">
@@ -6573,18 +6578,17 @@
       <c r="Z37" s="6" t="inlineStr">
         <is>
           <t>Q7 | Did you experience any of the following problems? | multi | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay; None of these | Validate: {"exclusive_option": "None of these"}
-Randomize
-Rules exercised: R9</t>
+Randomize</t>
         </is>
       </c>
       <c r="AA37" s="6" t="inlineStr">
         <is>
-          <t>Model-inferred. The questionnaire wrote this as prose rather than in a table, so Agent 1 read it with a model and raised it for sign-off. Confirm before relying on this test.</t>
-        </is>
-      </c>
-      <c r="AB37" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
+        </is>
+      </c>
+      <c r="AB37" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
         </is>
       </c>
       <c r="AC37" s="8" t="inlineStr">
@@ -6594,12 +6598,12 @@
       </c>
       <c r="AD37" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the order varies, only that nothing was lost or repeated. Order is a separate test needing several runs.</t>
         </is>
       </c>
       <c r="AE37" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
       </c>
     </row>
@@ -6614,22 +6618,22 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>TC-FT31</t>
+          <t>TC-ST02</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>FOCUSED</t>
+          <t>STATEFUL</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>4. Randomization</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>8. Implementation Conformance</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -6639,17 +6643,17 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Q7 blocks a blank answer</t>
+          <t>Q7 genuinely varies its option order</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>Prove Q7 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a multi question.</t>
+          <t>Prove Q7 is genuinely shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on.</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Without a genuine shuffle the option order biases the answers, and without the recorded order the answers cannot be corrected later.</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
@@ -6659,7 +6663,7 @@
       </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q7.</t>
+          <t>Run this same path 5 times and compare the recorded option order between runs.</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr">
@@ -6670,12 +6674,12 @@
       <c r="N38" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor
-then: At Q7, select nothing at all, then submit.</t>
+then: At Q7, tick 1 option (Dropped calls), then submit.</t>
         </is>
       </c>
       <c r="O38" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P38" s="6" t="inlineStr">
@@ -6685,17 +6689,17 @@
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
-          <t>At Q7, select nothing at all, then submit.</t>
+          <t>At Q7, tick 1 option (Dropped calls), then submit.</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7  (refused at Q7; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S38" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T38" s="6" t="inlineStr">
@@ -6705,23 +6709,22 @@
       </c>
       <c r="U38" s="6" t="inlineStr">
         <is>
-          <t>Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V38" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W38" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q7</t>
+          <t>1. the option order at Q7 is NOT identical on every run</t>
         </is>
       </c>
       <c r="X38" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y38" s="6" t="inlineStr">
@@ -6740,9 +6743,9 @@
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB38" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
+      <c r="AB38" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
         </is>
       </c>
       <c r="AC38" s="8" t="inlineStr">
@@ -6752,12 +6755,12 @@
       </c>
       <c r="AD38" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove any particular order is correct, only that the order is not fixed.</t>
         </is>
       </c>
       <c r="AE38" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
       </c>
     </row>
@@ -6767,12 +6770,12 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>TC-FT32</t>
+          <t>TC-FT31</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -6782,42 +6785,42 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>4. Randomization</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>8. Implementation Conformance</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Q7 shuffles without losing an option</t>
+          <t>Q8 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>Prove Q7 still presents all 6 of its options when shuffled, with none dropped and none repeated.</t>
+          <t>Prove that answering Q8 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>Without a genuine shuffle the option order biases the answers, and without the recorded order the answers cannot be corrected later.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q7.</t>
+          <t>Travel path P06 (Completing respondent — Q7=Support delay; Q9=No) as far as Q8.</t>
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr">
@@ -6827,8 +6830,8 @@
       </c>
       <c r="N39" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor
-then: At Q7, tick 1 option (Dropped calls), then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O39" s="6" t="inlineStr">
@@ -6838,27 +6841,27 @@
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
+          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>At Q7, tick 1 option (Dropped calls), then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S39" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T39" s="6" t="inlineStr">
         <is>
-          <t>Q8, Q9, Q10</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="U39" s="6" t="inlineStr">
@@ -6873,8 +6876,8 @@
       </c>
       <c r="W39" s="6" t="inlineStr">
         <is>
-          <t>1. Q7 shows exactly 6 options, none missing or repeated
-2. the options shown at Q7 are exactly: Coverage gap, Dropped calls, None of these, Slow data, Support delay, Unexpected charge</t>
+          <t>1. Q8 is on screen
+2. the next question shown is Q9</t>
         </is>
       </c>
       <c r="X39" s="6" t="inlineStr">
@@ -6889,13 +6892,13 @@
       </c>
       <c r="Z39" s="6" t="inlineStr">
         <is>
-          <t>Q7 | Did you experience any of the following problems? | multi | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay; None of these | Validate: {"exclusive_option": "None of these"}
-Randomize</t>
+          <t>Q8 | Which problem had the greatest impact? | single | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay | Show if: Q7 contains any problem
+Show only options selected at Q7.</t>
         </is>
       </c>
       <c r="AA39" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Model-inferred. The questionnaire wrote this as prose rather than in a table, so Agent 1 read it with a model and raised it for sign-off. Confirm before relying on this test.</t>
         </is>
       </c>
       <c r="AB39" s="10" t="inlineStr">
@@ -6910,7 +6913,7 @@
       </c>
       <c r="AD39" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the order varies, only that nothing was lost or repeated. Order is a separate test needing several runs.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE39" s="6" t="inlineStr">
@@ -6925,57 +6928,57 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>TC-ST02</t>
+          <t>TC-FT32</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>STATEFUL</t>
+          <t>FOCUSED</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>4. Randomization</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>8. Implementation Conformance</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Q7 genuinely varies its option order</t>
+          <t>Q8 is shown when its condition is met</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>Prove Q7 is genuinely shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on.</t>
+          <t>Prove Q8 IS shown when its display rule is satisfied. The rule is: Q7 contains any problem</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>Without a genuine shuffle the option order biases the answers, and without the recorded order the answers cannot be corrected later.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr">
         <is>
-          <t>Run this same path 5 times and compare the recorded option order between runs.</t>
+          <t>Travel path P06 (Completing respondent — Q7=Support delay; Q9=No) as far as Q8.</t>
         </is>
       </c>
       <c r="M40" s="6" t="inlineStr">
@@ -6985,8 +6988,8 @@
       </c>
       <c r="N40" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor
-then: At Q7, tick 1 option (Dropped calls), then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls
+then: At Q8, choose “Dropped calls”, then submit.</t>
         </is>
       </c>
       <c r="O40" s="6" t="inlineStr">
@@ -6996,27 +6999,27 @@
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
+          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
-          <t>At Q7, tick 1 option (Dropped calls), then submit.</t>
+          <t>At Q8, choose “Dropped calls”, then submit.</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S40" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T40" s="6" t="inlineStr">
         <is>
-          <t>Q8, Q9, Q10</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="U40" s="6" t="inlineStr">
@@ -7031,7 +7034,7 @@
       </c>
       <c r="W40" s="6" t="inlineStr">
         <is>
-          <t>1. the option order at Q7 is NOT identical on every run</t>
+          <t>1. Q8 is on screen</t>
         </is>
       </c>
       <c r="X40" s="6" t="inlineStr">
@@ -7046,13 +7049,14 @@
       </c>
       <c r="Z40" s="6" t="inlineStr">
         <is>
-          <t>Q7 | Did you experience any of the following problems? | multi | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay; None of these | Validate: {"exclusive_option": "None of these"}
-Randomize</t>
+          <t>Q8 | Which problem had the greatest impact? | single | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay | Show if: Q7 contains any problem
+Show only options selected at Q7.
+Rules exercised: R4</t>
         </is>
       </c>
       <c r="AA40" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Model-inferred. The questionnaire wrote this as prose rather than in a table, so Agent 1 read it with a model and raised it for sign-off. Confirm before relying on this test.</t>
         </is>
       </c>
       <c r="AB40" s="10" t="inlineStr">
@@ -7067,7 +7071,7 @@
       </c>
       <c r="AD40" s="6" t="inlineStr">
         <is>
-          <t>It does not prove any particular order is correct, only that the order is not fixed.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE40" s="6" t="inlineStr">
@@ -7102,7 +7106,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -7112,12 +7116,12 @@
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Q8 accepts a normal answer and the survey moves on</t>
+          <t>Q8 is not shown when its condition is not met</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q8 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q8 is NOT shown when its display rule is not satisfied. The rule is: Q7 contains any problem</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
@@ -7142,13 +7146,13 @@
       </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = None of these
+then: After submitting Q7, look for Q8 on the next page. Do not answer it.</t>
         </is>
       </c>
       <c r="O41" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>VALID_TYPICAL (the branch that hides the question)</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
@@ -7158,17 +7162,17 @@
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>After submitting Q7, look for Q8 on the next page. Do not answer it.</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S41" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T41" s="6" t="inlineStr">
@@ -7178,7 +7182,7 @@
       </c>
       <c r="U41" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q8, Q9, Q10</t>
         </is>
       </c>
       <c r="V41" s="6" t="inlineStr">
@@ -7188,8 +7192,8 @@
       </c>
       <c r="W41" s="6" t="inlineStr">
         <is>
-          <t>1. Q8 is on screen
-2. the next question shown is Q9</t>
+          <t>1. Q8 is NOT on screen
+2. the respondent carries on rather than being screened out or finished</t>
         </is>
       </c>
       <c r="X41" s="6" t="inlineStr">
@@ -7205,7 +7209,8 @@
       <c r="Z41" s="6" t="inlineStr">
         <is>
           <t>Q8 | Which problem had the greatest impact? | single | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay | Show if: Q7 contains any problem
-Show only options selected at Q7.</t>
+Show only options selected at Q7.
+Rules exercised: R4</t>
         </is>
       </c>
       <c r="AA41" s="6" t="inlineStr">
@@ -7225,12 +7230,12 @@
       </c>
       <c r="AD41" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove why the question was absent beyond the display rule; the check confirms the respondent was still travelling and had not been screened out. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE41" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
+          <t>Leans on an unconfirmed reading: multi_equality, rule_precedence</t>
         </is>
       </c>
     </row>
@@ -7255,12 +7260,12 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -7270,22 +7275,22 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Q8 is shown when its condition is met</t>
+          <t>Q8 blocks a blank answer</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 IS shown when its display rule is satisfied. The rule is: Q7 contains any problem</t>
+          <t>Prove Q8 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
@@ -7301,12 +7306,12 @@
       <c r="N42" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls
-then: At Q8, choose “Dropped calls”, then submit.</t>
+then: At Q8, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O42" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P42" s="6" t="inlineStr">
@@ -7316,17 +7321,17 @@
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
-          <t>At Q8, choose “Dropped calls”, then submit.</t>
+          <t>At Q8, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8  (refused at Q8; respondent stays put)</t>
         </is>
       </c>
       <c r="S42" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T42" s="6" t="inlineStr">
@@ -7336,22 +7341,23 @@
       </c>
       <c r="U42" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V42" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W42" s="6" t="inlineStr">
         <is>
-          <t>1. Q8 is on screen</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q8</t>
         </is>
       </c>
       <c r="X42" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y42" s="6" t="inlineStr">
@@ -7362,8 +7368,7 @@
       <c r="Z42" s="6" t="inlineStr">
         <is>
           <t>Q8 | Which problem had the greatest impact? | single | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay | Show if: Q7 contains any problem
-Show only options selected at Q7.
-Rules exercised: R4</t>
+Show only options selected at Q7.</t>
         </is>
       </c>
       <c r="AA42" s="6" t="inlineStr">
@@ -7383,7 +7388,7 @@
       </c>
       <c r="AD42" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE42" s="6" t="inlineStr">
@@ -7413,14 +7418,14 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
+          <t>3. Dependency / Piping</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
           <t>1. Flow / Routing</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>10. Negative / Robustness</t>
-        </is>
-      </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
           <t>P06</t>
@@ -7428,17 +7433,17 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Q8 is not shown when its condition is not met</t>
+          <t>Q8 offers only the options chosen at Q7</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 is NOT shown when its display rule is not satisfied. The rule is: Q7 contains any problem</t>
+          <t>Prove Q8's option list is built from the answer given at Q7, so the respondent is only asked about what they actually chose.</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A question that quietly shows the wrong options asks the respondent about something they never selected.</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
@@ -7458,13 +7463,13 @@
       </c>
       <c r="N43" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = None of these
-then: After submitting Q7, look for Q8 on the next page. Do not answer it.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls
+then: At Q8, choose “Dropped calls”, then submit.</t>
         </is>
       </c>
       <c r="O43" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL (the branch that hides the question)</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P43" s="6" t="inlineStr">
@@ -7474,17 +7479,17 @@
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>After submitting Q7, look for Q8 on the next page. Do not answer it.</t>
+          <t>At Q8, choose “Dropped calls”, then submit.</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S43" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T43" s="6" t="inlineStr">
@@ -7494,7 +7499,7 @@
       </c>
       <c r="U43" s="6" t="inlineStr">
         <is>
-          <t>Q8, Q9, Q10</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V43" s="6" t="inlineStr">
@@ -7504,8 +7509,7 @@
       </c>
       <c r="W43" s="6" t="inlineStr">
         <is>
-          <t>1. Q8 is NOT on screen
-2. the respondent carries on rather than being screened out or finished</t>
+          <t>1. Q8 offers exactly: A001</t>
         </is>
       </c>
       <c r="X43" s="6" t="inlineStr">
@@ -7521,13 +7525,12 @@
       <c r="Z43" s="6" t="inlineStr">
         <is>
           <t>Q8 | Which problem had the greatest impact? | single | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay | Show if: Q7 contains any problem
-Show only options selected at Q7.
-Rules exercised: R4</t>
+Show only options selected at Q7.</t>
         </is>
       </c>
       <c r="AA43" s="6" t="inlineStr">
         <is>
-          <t>Model-inferred. The questionnaire wrote this as prose rather than in a table, so Agent 1 read it with a model and raised it for sign-off. Confirm before relying on this test.</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
       <c r="AB43" s="10" t="inlineStr">
@@ -7542,12 +7545,12 @@
       </c>
       <c r="AD43" s="6" t="inlineStr">
         <is>
-          <t>It does not prove why the question was absent beyond the display rule; the check confirms the respondent was still travelling and had not been screened out. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE43" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality, rule_precedence</t>
+          <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
       </c>
     </row>
@@ -7572,12 +7575,12 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>9. Rule Interaction</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -7587,17 +7590,17 @@
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Q8 blocks a blank answer</t>
+          <t>Q8 is shown and reflects its dependency on Q7 at the same time</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove Q8 is shown by its display rule and simultaneously reflects its dependency on Q7. Each mechanism can be correct alone and still disagree together.</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Individually correct rules can combine into behaviour neither one describes on its own.</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
@@ -7618,12 +7621,12 @@
       <c r="N44" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls
-then: At Q8, select nothing at all, then submit.</t>
+then: At Q8, choose “Dropped calls”, then submit.</t>
         </is>
       </c>
       <c r="O44" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P44" s="6" t="inlineStr">
@@ -7633,17 +7636,17 @@
       </c>
       <c r="Q44" s="6" t="inlineStr">
         <is>
-          <t>At Q8, select nothing at all, then submit.</t>
+          <t>At Q8, choose “Dropped calls”, then submit.</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8  (refused at Q8; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S44" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T44" s="6" t="inlineStr">
@@ -7653,23 +7656,23 @@
       </c>
       <c r="U44" s="6" t="inlineStr">
         <is>
-          <t>Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V44" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W44" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q8</t>
+          <t>1. Q8 is on screen
+2. Q8's wording includes: Dropped calls</t>
         </is>
       </c>
       <c r="X44" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y44" s="6" t="inlineStr">
@@ -7685,7 +7688,7 @@
       </c>
       <c r="AA44" s="6" t="inlineStr">
         <is>
-          <t>Model-inferred. The questionnaire wrote this as prose rather than in a table, so Agent 1 read it with a model and raised it for sign-off. Confirm before relying on this test.</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
       <c r="AB44" s="10" t="inlineStr">
@@ -7700,7 +7703,7 @@
       </c>
       <c r="AD44" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE44" s="6" t="inlineStr">
@@ -7715,7 +7718,7 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -7730,12 +7733,12 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -7745,17 +7748,17 @@
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>Q8 offers only the options chosen at Q7</t>
+          <t>Q9 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8's option list is built from the answer given at Q7, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove that answering Q9 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>A question that quietly shows the wrong options asks the respondent about something they never selected.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
@@ -7765,7 +7768,7 @@
       </c>
       <c r="L45" s="6" t="inlineStr">
         <is>
-          <t>Travel path P06 (Completing respondent — Q7=Support delay; Q9=No) as far as Q8.</t>
+          <t>Travel path P06 (Completing respondent — Q7=Support delay; Q9=No) as far as Q9.</t>
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr">
@@ -7775,8 +7778,8 @@
       </c>
       <c r="N45" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls
-then: At Q8, choose “Dropped calls”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O45" s="6" t="inlineStr">
@@ -7786,22 +7789,22 @@
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
+          <t>Every answer before Q9 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q9 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
-          <t>At Q8, choose “Dropped calls”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S45" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T45" s="6" t="inlineStr">
@@ -7821,7 +7824,8 @@
       </c>
       <c r="W45" s="6" t="inlineStr">
         <is>
-          <t>1. Q8 offers exactly: A001</t>
+          <t>1. Q9 is on screen
+2. the next question shown is Q10</t>
         </is>
       </c>
       <c r="X45" s="6" t="inlineStr">
@@ -7836,13 +7840,12 @@
       </c>
       <c r="Z45" s="6" t="inlineStr">
         <is>
-          <t>Q8 | Which problem had the greatest impact? | single | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay | Show if: Q7 contains any problem
-Show only options selected at Q7.</t>
+          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
         </is>
       </c>
       <c r="AA45" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Model-inferred. The questionnaire wrote this as prose rather than in a table, so Agent 1 read it with a model and raised it for sign-off. Confirm before relying on this test.</t>
         </is>
       </c>
       <c r="AB45" s="10" t="inlineStr">
@@ -7857,7 +7860,7 @@
       </c>
       <c r="AD45" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE45" s="6" t="inlineStr">
@@ -7872,7 +7875,7 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
@@ -7887,12 +7890,12 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>9. Rule Interaction</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -7902,27 +7905,27 @@
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>Q8 is shown and reflects its dependency on Q7 at the same time</t>
+          <t>Q9 is shown when its condition is met</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 is shown by its display rule and simultaneously reflects its dependency on Q7. Each mechanism can be correct alone and still disagree together.</t>
+          <t>Prove Q9 IS shown when its display rule is satisfied. The rule is: Q7 contains any problem</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>Individually correct rules can combine into behaviour neither one describes on its own.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr">
         <is>
-          <t>Travel path P06 (Completing respondent — Q7=Support delay; Q9=No) as far as Q8.</t>
+          <t>Travel path P06 (Completing respondent — Q7=Support delay; Q9=No) as far as Q9.</t>
         </is>
       </c>
       <c r="M46" s="6" t="inlineStr">
@@ -7932,8 +7935,8 @@
       </c>
       <c r="N46" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls
-then: At Q8, choose “Dropped calls”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls
+then: At Q9, choose “Yes, fully”, then submit.</t>
         </is>
       </c>
       <c r="O46" s="6" t="inlineStr">
@@ -7943,22 +7946,22 @@
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
+          <t>Every answer before Q9 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q9 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q46" s="6" t="inlineStr">
         <is>
-          <t>At Q8, choose “Dropped calls”, then submit.</t>
+          <t>At Q9, choose “Yes, fully”, then submit.</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S46" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T46" s="6" t="inlineStr">
@@ -7978,8 +7981,7 @@
       </c>
       <c r="W46" s="6" t="inlineStr">
         <is>
-          <t>1. Q8 is on screen
-2. Q8's wording includes: Dropped calls</t>
+          <t>1. Q9 is on screen</t>
         </is>
       </c>
       <c r="X46" s="6" t="inlineStr">
@@ -7994,13 +7996,13 @@
       </c>
       <c r="Z46" s="6" t="inlineStr">
         <is>
-          <t>Q8 | Which problem had the greatest impact? | single | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay | Show if: Q7 contains any problem
-Show only options selected at Q7.</t>
+          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem
+Rules exercised: R5</t>
         </is>
       </c>
       <c r="AA46" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Model-inferred. The questionnaire wrote this as prose rather than in a table, so Agent 1 read it with a model and raised it for sign-off. Confirm before relying on this test.</t>
         </is>
       </c>
       <c r="AB46" s="10" t="inlineStr">
@@ -8050,7 +8052,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -8060,12 +8062,12 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Q9 accepts a normal answer and the survey moves on</t>
+          <t>Q9 is not shown when its condition is not met</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q9 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q9 is NOT shown when its display rule is not satisfied. The rule is: Q7 contains any problem</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
@@ -8090,13 +8092,13 @@
       </c>
       <c r="N47" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = None of these
+then: After submitting Q7, look for Q9 on the next page. Do not answer it.</t>
         </is>
       </c>
       <c r="O47" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>VALID_TYPICAL (the branch that hides the question)</t>
         </is>
       </c>
       <c r="P47" s="6" t="inlineStr">
@@ -8106,17 +8108,17 @@
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>After submitting Q7, look for Q9 on the next page. Do not answer it.</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S47" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T47" s="6" t="inlineStr">
@@ -8126,7 +8128,7 @@
       </c>
       <c r="U47" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q8, Q9, Q10</t>
         </is>
       </c>
       <c r="V47" s="6" t="inlineStr">
@@ -8136,8 +8138,8 @@
       </c>
       <c r="W47" s="6" t="inlineStr">
         <is>
-          <t>1. Q9 is on screen
-2. the next question shown is Q10</t>
+          <t>1. Q9 is NOT on screen
+2. the respondent carries on rather than being screened out or finished</t>
         </is>
       </c>
       <c r="X47" s="6" t="inlineStr">
@@ -8152,7 +8154,8 @@
       </c>
       <c r="Z47" s="6" t="inlineStr">
         <is>
-          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
+          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem
+Rules exercised: R5</t>
         </is>
       </c>
       <c r="AA47" s="6" t="inlineStr">
@@ -8172,12 +8175,12 @@
       </c>
       <c r="AD47" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove why the question was absent beyond the display rule; the check confirms the respondent was still travelling and had not been screened out. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE47" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
+          <t>Leans on an unconfirmed reading: multi_equality, rule_precedence</t>
         </is>
       </c>
     </row>
@@ -8217,12 +8220,12 @@
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>Q9 is shown when its condition is met</t>
+          <t>R8 jumps forward when its condition is met</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>Prove Q9 IS shown when its display rule is satisfied. The rule is: Q7 contains any problem</t>
+          <t>Prove R8 jumps to Q11. The rule is: Q9 == 'No'</t>
         </is>
       </c>
       <c r="J48" s="6" t="inlineStr">
@@ -8248,7 +8251,7 @@
       <c r="N48" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls
-then: At Q9, choose “Yes, fully”, then submit.</t>
+then: At Q9, choose “No”, then submit.</t>
         </is>
       </c>
       <c r="O48" s="6" t="inlineStr">
@@ -8263,17 +8266,17 @@
       </c>
       <c r="Q48" s="6" t="inlineStr">
         <is>
-          <t>At Q9, choose “Yes, fully”, then submit.</t>
+          <t>At Q9, choose “No”, then submit.</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S48" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T48" s="6" t="inlineStr">
@@ -8283,7 +8286,7 @@
       </c>
       <c r="U48" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="V48" s="6" t="inlineStr">
@@ -8293,7 +8296,7 @@
       </c>
       <c r="W48" s="6" t="inlineStr">
         <is>
-          <t>1. Q9 is on screen</t>
+          <t>1. the next question shown is Q11</t>
         </is>
       </c>
       <c r="X48" s="6" t="inlineStr">
@@ -8309,12 +8312,12 @@
       <c r="Z48" s="6" t="inlineStr">
         <is>
           <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem
-Rules exercised: R5</t>
+Rules exercised: R8</t>
         </is>
       </c>
       <c r="AA48" s="6" t="inlineStr">
         <is>
-          <t>Model-inferred. The questionnaire wrote this as prose rather than in a table, so Agent 1 read it with a model and raised it for sign-off. Confirm before relying on this test.</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
       <c r="AB48" s="10" t="inlineStr">
@@ -8334,7 +8337,7 @@
       </c>
       <c r="AE48" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
+          <t>Leans on an unconfirmed reading: multi_equality, rule_precedence</t>
         </is>
       </c>
     </row>
@@ -8374,12 +8377,12 @@
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>Q9 is not shown when its condition is not met</t>
+          <t>R8 does not jump when its condition is not met</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>Prove Q9 is NOT shown when its display rule is not satisfied. The rule is: Q7 contains any problem</t>
+          <t>Prove R8 does not jump and the respondent continues in sequence. The rule is: Q9 == 'No'</t>
         </is>
       </c>
       <c r="J49" s="6" t="inlineStr">
@@ -8404,13 +8407,13 @@
       </c>
       <c r="N49" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = None of these
-then: After submitting Q7, look for Q9 on the next page. Do not answer it.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls
+then: At Q9, choose “Yes, fully”, then submit.</t>
         </is>
       </c>
       <c r="O49" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL (the branch that hides the question)</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P49" s="6" t="inlineStr">
@@ -8420,17 +8423,17 @@
       </c>
       <c r="Q49" s="6" t="inlineStr">
         <is>
-          <t>After submitting Q7, look for Q9 on the next page. Do not answer it.</t>
+          <t>At Q9, choose “Yes, fully”, then submit.</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S49" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T49" s="6" t="inlineStr">
@@ -8440,7 +8443,7 @@
       </c>
       <c r="U49" s="6" t="inlineStr">
         <is>
-          <t>Q8, Q9, Q10</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V49" s="6" t="inlineStr">
@@ -8450,8 +8453,7 @@
       </c>
       <c r="W49" s="6" t="inlineStr">
         <is>
-          <t>1. Q9 is NOT on screen
-2. the respondent carries on rather than being screened out or finished</t>
+          <t>1. the next question shown is Q10</t>
         </is>
       </c>
       <c r="X49" s="6" t="inlineStr">
@@ -8467,12 +8469,12 @@
       <c r="Z49" s="6" t="inlineStr">
         <is>
           <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem
-Rules exercised: R5</t>
+Rules exercised: R8</t>
         </is>
       </c>
       <c r="AA49" s="6" t="inlineStr">
         <is>
-          <t>Model-inferred. The questionnaire wrote this as prose rather than in a table, so Agent 1 read it with a model and raised it for sign-off. Confirm before relying on this test.</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
       <c r="AB49" s="10" t="inlineStr">
@@ -8487,12 +8489,12 @@
       </c>
       <c r="AD49" s="6" t="inlineStr">
         <is>
-          <t>It does not prove why the question was absent beyond the display rule; the check confirms the respondent was still travelling and had not been screened out. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE49" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality, rule_precedence</t>
+          <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
       </c>
     </row>
@@ -8517,12 +8519,12 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
@@ -8532,22 +8534,22 @@
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>R8 jumps forward when its condition is met</t>
+          <t>Q9 blocks a blank answer</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>Prove R8 jumps to Q11. The rule is: Q9 == 'No'</t>
+          <t>Prove Q9 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr">
@@ -8563,12 +8565,12 @@
       <c r="N50" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls
-then: At Q9, choose “No”, then submit.</t>
+then: At Q9, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O50" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P50" s="6" t="inlineStr">
@@ -8578,17 +8580,17 @@
       </c>
       <c r="Q50" s="6" t="inlineStr">
         <is>
-          <t>At Q9, choose “No”, then submit.</t>
+          <t>At Q9, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9  (refused at Q9; respondent stays put)</t>
         </is>
       </c>
       <c r="S50" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9</t>
         </is>
       </c>
       <c r="T50" s="6" t="inlineStr">
@@ -8598,22 +8600,23 @@
       </c>
       <c r="U50" s="6" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V50" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W50" s="6" t="inlineStr">
         <is>
-          <t>1. the next question shown is Q11</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q9</t>
         </is>
       </c>
       <c r="X50" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y50" s="6" t="inlineStr">
@@ -8623,13 +8626,12 @@
       </c>
       <c r="Z50" s="6" t="inlineStr">
         <is>
-          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem
-Rules exercised: R8</t>
+          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
         </is>
       </c>
       <c r="AA50" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Model-inferred. The questionnaire wrote this as prose rather than in a table, so Agent 1 read it with a model and raised it for sign-off. Confirm before relying on this test.</t>
         </is>
       </c>
       <c r="AB50" s="10" t="inlineStr">
@@ -8644,12 +8646,12 @@
       </c>
       <c r="AD50" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE50" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality, rule_precedence</t>
+          <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
       </c>
     </row>
@@ -8674,12 +8676,12 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>3. Dependency / Piping</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
@@ -8689,22 +8691,22 @@
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>R8 does not jump when its condition is not met</t>
+          <t>Q9 quotes the answer given at Q7</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>Prove R8 does not jump and the respondent continues in sequence. The rule is: Q9 == 'No'</t>
+          <t>Prove Q9's wording is built from the answer given at Q7, so the respondent is only asked about what they actually chose.</t>
         </is>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr">
@@ -8740,12 +8742,12 @@
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S51" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T51" s="6" t="inlineStr">
@@ -8765,7 +8767,7 @@
       </c>
       <c r="W51" s="6" t="inlineStr">
         <is>
-          <t>1. the next question shown is Q10</t>
+          <t>1. Q9's wording includes: Dropped calls</t>
         </is>
       </c>
       <c r="X51" s="6" t="inlineStr">
@@ -8780,8 +8782,7 @@
       </c>
       <c r="Z51" s="6" t="inlineStr">
         <is>
-          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem
-Rules exercised: R8</t>
+          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
         </is>
       </c>
       <c r="AA51" s="6" t="inlineStr">
@@ -8831,12 +8832,12 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>9. Rule Interaction</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
@@ -8846,17 +8847,17 @@
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>Q9 blocks a blank answer</t>
+          <t>Q9 is shown and reflects its dependency on Q7 at the same time</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>Prove Q9 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove Q9 is shown by its display rule and simultaneously reflects its dependency on Q7. Each mechanism can be correct alone and still disagree together.</t>
         </is>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Individually correct rules can combine into behaviour neither one describes on its own.</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr">
@@ -8877,12 +8878,12 @@
       <c r="N52" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls
-then: At Q9, select nothing at all, then submit.</t>
+then: At Q9, choose “Yes, fully”, then submit.</t>
         </is>
       </c>
       <c r="O52" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P52" s="6" t="inlineStr">
@@ -8892,17 +8893,17 @@
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
-          <t>At Q9, select nothing at all, then submit.</t>
+          <t>At Q9, choose “Yes, fully”, then submit.</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9  (refused at Q9; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S52" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T52" s="6" t="inlineStr">
@@ -8912,23 +8913,23 @@
       </c>
       <c r="U52" s="6" t="inlineStr">
         <is>
-          <t>Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V52" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W52" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q9</t>
+          <t>1. Q9 is on screen
+2. Q9's wording includes: Dropped calls</t>
         </is>
       </c>
       <c r="X52" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y52" s="6" t="inlineStr">
@@ -8943,7 +8944,7 @@
       </c>
       <c r="AA52" s="6" t="inlineStr">
         <is>
-          <t>Model-inferred. The questionnaire wrote this as prose rather than in a table, so Agent 1 read it with a model and raised it for sign-off. Confirm before relying on this test.</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
       <c r="AB52" s="10" t="inlineStr">
@@ -8958,7 +8959,7 @@
       </c>
       <c r="AD52" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE52" s="6" t="inlineStr">
@@ -8973,7 +8974,7 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
@@ -8988,7 +8989,7 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -8998,32 +8999,32 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Q9 quotes the answer given at Q8</t>
+          <t>Q10 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>Prove Q9's wording is built from the answer given at Q8, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove that answering Q10 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr">
         <is>
-          <t>Travel path P06 (Completing respondent — Q7=Support delay; Q9=No) as far as Q9.</t>
+          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as Q10.</t>
         </is>
       </c>
       <c r="M53" s="6" t="inlineStr">
@@ -9033,8 +9034,8 @@
       </c>
       <c r="N53" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls
-then: At Q9, choose “Yes, fully”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O53" s="6" t="inlineStr">
@@ -9044,27 +9045,27 @@
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q9 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q9 is the one the claim turns on.</t>
+          <t>Every answer before Q10 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q10 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>At Q9, choose “Yes, fully”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S53" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T53" s="6" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U53" s="6" t="inlineStr">
@@ -9079,7 +9080,8 @@
       </c>
       <c r="W53" s="6" t="inlineStr">
         <is>
-          <t>1. Q9's wording includes: Dropped calls</t>
+          <t>1. Q10 is on screen
+2. the next question shown is Q11</t>
         </is>
       </c>
       <c r="X53" s="6" t="inlineStr">
@@ -9094,12 +9096,12 @@
       </c>
       <c r="Z53" s="6" t="inlineStr">
         <is>
-          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
+          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
       <c r="AA53" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
       <c r="AB53" s="10" t="inlineStr">
@@ -9114,7 +9116,7 @@
       </c>
       <c r="AD53" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE53" s="6" t="inlineStr">
@@ -9129,7 +9131,7 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
@@ -9144,42 +9146,42 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>9. Rule Interaction</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>Q9 is shown and reflects its dependency on Q8 at the same time</t>
+          <t>Q10 is shown when its condition is met</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>Prove Q9 is shown by its display rule and simultaneously reflects its dependency on Q8. Each mechanism can be correct alone and still disagree together.</t>
+          <t>Prove Q10 IS shown when its display rule is satisfied. The rule is: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>Individually correct rules can combine into behaviour neither one describes on its own.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L54" s="6" t="inlineStr">
         <is>
-          <t>Travel path P06 (Completing respondent — Q7=Support delay; Q9=No) as far as Q9.</t>
+          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as Q10.</t>
         </is>
       </c>
       <c r="M54" s="6" t="inlineStr">
@@ -9189,8 +9191,8 @@
       </c>
       <c r="N54" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls
-then: At Q9, choose “Yes, fully”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully
+then: At Q10, choose “Very poor”, then submit.</t>
         </is>
       </c>
       <c r="O54" s="6" t="inlineStr">
@@ -9200,27 +9202,27 @@
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q9 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q9 is the one the claim turns on.</t>
+          <t>Every answer before Q10 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q10 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
-          <t>At Q9, choose “Yes, fully”, then submit.</t>
+          <t>At Q10, choose “Very poor”, then submit.</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S54" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T54" s="6" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U54" s="6" t="inlineStr">
@@ -9235,8 +9237,7 @@
       </c>
       <c r="W54" s="6" t="inlineStr">
         <is>
-          <t>1. Q9 is on screen
-2. Q9's wording includes: Dropped calls</t>
+          <t>1. Q10 is on screen</t>
         </is>
       </c>
       <c r="X54" s="6" t="inlineStr">
@@ -9251,12 +9252,13 @@
       </c>
       <c r="Z54" s="6" t="inlineStr">
         <is>
-          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
+          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']
+Rules exercised: R7</t>
         </is>
       </c>
       <c r="AA54" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
       <c r="AB54" s="10" t="inlineStr">
@@ -9306,7 +9308,7 @@
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
@@ -9316,12 +9318,12 @@
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>Q10 accepts a normal answer and the survey moves on</t>
+          <t>Q10 is not shown when its condition is not met</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q10 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q10 is NOT shown when its display rule is not satisfied. The rule is: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr">
@@ -9346,13 +9348,13 @@
       </c>
       <c r="N55" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = No
+then: After submitting Q9, look for Q10 on the next page. Do not answer it.</t>
         </is>
       </c>
       <c r="O55" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>VALID_TYPICAL (the branch that hides the question)</t>
         </is>
       </c>
       <c r="P55" s="6" t="inlineStr">
@@ -9362,17 +9364,17 @@
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>After submitting Q9, look for Q10 on the next page. Do not answer it.</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S55" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T55" s="6" t="inlineStr">
@@ -9382,7 +9384,7 @@
       </c>
       <c r="U55" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="V55" s="6" t="inlineStr">
@@ -9392,8 +9394,8 @@
       </c>
       <c r="W55" s="6" t="inlineStr">
         <is>
-          <t>1. Q10 is on screen
-2. the next question shown is Q11</t>
+          <t>1. Q10 is NOT on screen
+2. the respondent carries on rather than being screened out or finished</t>
         </is>
       </c>
       <c r="X55" s="6" t="inlineStr">
@@ -9408,7 +9410,8 @@
       </c>
       <c r="Z55" s="6" t="inlineStr">
         <is>
-          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
+          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']
+Rules exercised: R7</t>
         </is>
       </c>
       <c r="AA55" s="6" t="inlineStr">
@@ -9428,12 +9431,12 @@
       </c>
       <c r="AD55" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove why the question was absent beyond the display rule; the check confirms the respondent was still travelling and had not been screened out. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE55" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
+          <t>Leans on an unconfirmed reading: multi_equality, rule_precedence</t>
         </is>
       </c>
     </row>
@@ -9458,12 +9461,12 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
@@ -9473,22 +9476,22 @@
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Q10 is shown when its condition is met</t>
+          <t>Q10 blocks a blank answer</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>Prove Q10 IS shown when its display rule is satisfied. The rule is: Q9 in ['Yes, fully','Yes, partly']</t>
+          <t>Prove Q10 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K56" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L56" s="6" t="inlineStr">
@@ -9504,12 +9507,12 @@
       <c r="N56" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully
-then: At Q10, choose “Very poor”, then submit.</t>
+then: At Q10, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O56" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P56" s="6" t="inlineStr">
@@ -9519,17 +9522,17 @@
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
-          <t>At Q10, choose “Very poor”, then submit.</t>
+          <t>At Q10, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10  (refused at Q10; respondent stays put)</t>
         </is>
       </c>
       <c r="S56" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10</t>
         </is>
       </c>
       <c r="T56" s="6" t="inlineStr">
@@ -9539,22 +9542,23 @@
       </c>
       <c r="U56" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V56" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W56" s="6" t="inlineStr">
         <is>
-          <t>1. Q10 is on screen</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q10</t>
         </is>
       </c>
       <c r="X56" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y56" s="6" t="inlineStr">
@@ -9564,8 +9568,7 @@
       </c>
       <c r="Z56" s="6" t="inlineStr">
         <is>
-          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']
-Rules exercised: R7</t>
+          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
       <c r="AA56" s="6" t="inlineStr">
@@ -9585,7 +9588,7 @@
       </c>
       <c r="AD56" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE56" s="6" t="inlineStr">
@@ -9615,12 +9618,12 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>3. Dependency / Piping</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
@@ -9630,22 +9633,22 @@
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>Q10 is not shown when its condition is not met</t>
+          <t>Q10 quotes the answer given at Q9</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>Prove Q10 is NOT shown when its display rule is not satisfied. The rule is: Q9 in ['Yes, fully','Yes, partly']</t>
+          <t>Prove Q10's wording is built from the answer given at Q9, so the respondent is only asked about what they actually chose.</t>
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L57" s="6" t="inlineStr">
@@ -9660,13 +9663,13 @@
       </c>
       <c r="N57" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = No
-then: After submitting Q9, look for Q10 on the next page. Do not answer it.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully
+then: At Q10, choose “Very poor”, then submit.</t>
         </is>
       </c>
       <c r="O57" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL (the branch that hides the question)</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P57" s="6" t="inlineStr">
@@ -9676,17 +9679,17 @@
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
-          <t>After submitting Q9, look for Q10 on the next page. Do not answer it.</t>
+          <t>At Q10, choose “Very poor”, then submit.</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S57" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T57" s="6" t="inlineStr">
@@ -9696,7 +9699,7 @@
       </c>
       <c r="U57" s="6" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V57" s="6" t="inlineStr">
@@ -9706,8 +9709,7 @@
       </c>
       <c r="W57" s="6" t="inlineStr">
         <is>
-          <t>1. Q10 is NOT on screen
-2. the respondent carries on rather than being screened out or finished</t>
+          <t>1. Q10's wording includes: Yes, fully</t>
         </is>
       </c>
       <c r="X57" s="6" t="inlineStr">
@@ -9722,13 +9724,12 @@
       </c>
       <c r="Z57" s="6" t="inlineStr">
         <is>
-          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']
-Rules exercised: R7</t>
+          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
       <c r="AA57" s="6" t="inlineStr">
         <is>
-          <t>Derived by rule from the questionnaire's own tables.</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
       <c r="AB57" s="10" t="inlineStr">
@@ -9743,12 +9744,12 @@
       </c>
       <c r="AD57" s="6" t="inlineStr">
         <is>
-          <t>It does not prove why the question was absent beyond the display rule; the check confirms the respondent was still travelling and had not been screened out. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE57" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality, rule_precedence</t>
+          <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
       </c>
     </row>
@@ -9773,12 +9774,12 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>9. Rule Interaction</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -9788,17 +9789,17 @@
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>Q10 blocks a blank answer</t>
+          <t>Q10 is shown and reflects its dependency on Q9 at the same time</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>Prove Q10 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove Q10 is shown by its display rule and simultaneously reflects its dependency on Q9. Each mechanism can be correct alone and still disagree together.</t>
         </is>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Individually correct rules can combine into behaviour neither one describes on its own.</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
@@ -9819,12 +9820,12 @@
       <c r="N58" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully
-then: At Q10, select nothing at all, then submit.</t>
+then: At Q10, choose “Very poor”, then submit.</t>
         </is>
       </c>
       <c r="O58" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P58" s="6" t="inlineStr">
@@ -9834,17 +9835,17 @@
       </c>
       <c r="Q58" s="6" t="inlineStr">
         <is>
-          <t>At Q10, select nothing at all, then submit.</t>
+          <t>At Q10, choose “Very poor”, then submit.</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10  (refused at Q10; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S58" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T58" s="6" t="inlineStr">
@@ -9854,23 +9855,23 @@
       </c>
       <c r="U58" s="6" t="inlineStr">
         <is>
-          <t>Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V58" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W58" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q10</t>
+          <t>1. Q10 is on screen
+2. Q10's wording includes: Yes, fully</t>
         </is>
       </c>
       <c r="X58" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y58" s="6" t="inlineStr">
@@ -9885,7 +9886,7 @@
       </c>
       <c r="AA58" s="6" t="inlineStr">
         <is>
-          <t>Derived by rule from the questionnaire's own tables.</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
       <c r="AB58" s="10" t="inlineStr">
@@ -9900,7 +9901,7 @@
       </c>
       <c r="AD58" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE58" s="6" t="inlineStr">
@@ -9915,7 +9916,7 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Q11</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -9930,7 +9931,7 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -9940,32 +9941,32 @@
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>Q10 quotes the answer given at Q9</t>
+          <t>Q11 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>Prove Q10's wording is built from the answer given at Q9, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove that answering Q11 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L59" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as Q10.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q11.</t>
         </is>
       </c>
       <c r="M59" s="6" t="inlineStr">
@@ -9975,8 +9976,8 @@
       </c>
       <c r="N59" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully
-then: At Q10, choose “Very poor”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O59" s="6" t="inlineStr">
@@ -9986,34 +9987,34 @@
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q10 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q10 is the one the claim turns on.</t>
+          <t>Every answer before Q11 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q11 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q59" s="6" t="inlineStr">
         <is>
-          <t>At Q10, choose “Very poor”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S59" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T59" s="6" t="inlineStr">
         <is>
+          <t>Q8, Q9, Q10</t>
+        </is>
+      </c>
+      <c r="U59" s="6" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U59" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="V59" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
@@ -10021,7 +10022,8 @@
       </c>
       <c r="W59" s="6" t="inlineStr">
         <is>
-          <t>1. Q10's wording includes: Yes, fully</t>
+          <t>1. Q11 is on screen
+2. the next question shown is Q12</t>
         </is>
       </c>
       <c r="X59" s="6" t="inlineStr">
@@ -10036,7 +10038,7 @@
       </c>
       <c r="Z59" s="6" t="inlineStr">
         <is>
-          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
+          <t>Q11 | How likely are you to recommend the provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
         </is>
       </c>
       <c r="AA59" s="6" t="inlineStr">
@@ -10056,7 +10058,7 @@
       </c>
       <c r="AD59" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE59" s="6" t="inlineStr">
@@ -10071,7 +10073,7 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Q11</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
@@ -10086,32 +10088,32 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>9. Rule Interaction</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>Q10 is shown and reflects its dependency on Q9 at the same time</t>
+          <t>Q11 blocks a blank answer</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>Prove Q10 is shown by its display rule and simultaneously reflects its dependency on Q9. Each mechanism can be correct alone and still disagree together.</t>
+          <t>Prove Q11 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>Individually correct rules can combine into behaviour neither one describes on its own.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K60" s="6" t="inlineStr">
@@ -10121,7 +10123,7 @@
       </c>
       <c r="L60" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as Q10.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q11.</t>
         </is>
       </c>
       <c r="M60" s="6" t="inlineStr">
@@ -10131,59 +10133,59 @@
       </c>
       <c r="N60" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully
-then: At Q10, choose “Very poor”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor
+then: At Q11, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O60" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q10 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q10 is the one the claim turns on.</t>
+          <t>Every answer before Q11 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q11 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q60" s="6" t="inlineStr">
         <is>
-          <t>At Q10, choose “Very poor”, then submit.</t>
+          <t>At Q11, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11  (refused at Q11; respondent stays put)</t>
         </is>
       </c>
       <c r="S60" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11</t>
         </is>
       </c>
       <c r="T60" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q8, Q9, Q10</t>
         </is>
       </c>
       <c r="U60" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V60" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W60" s="6" t="inlineStr">
         <is>
-          <t>1. Q10 is on screen
-2. Q10's wording includes: Yes, fully</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q11</t>
         </is>
       </c>
       <c r="X60" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y60" s="6" t="inlineStr">
@@ -10193,7 +10195,7 @@
       </c>
       <c r="Z60" s="6" t="inlineStr">
         <is>
-          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
+          <t>Q11 | How likely are you to recommend the provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
         </is>
       </c>
       <c r="AA60" s="6" t="inlineStr">
@@ -10213,7 +10215,7 @@
       </c>
       <c r="AD60" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE60" s="6" t="inlineStr">
@@ -10243,7 +10245,7 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>3. Dependency / Piping</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -10258,22 +10260,22 @@
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Q11 accepts a normal answer and the survey moves on</t>
+          <t>Q11 quotes the answer given at Q1</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q11 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q11's wording is built from the answer given at Q1, so the respondent is only asked about what they actually chose.</t>
         </is>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr">
@@ -10288,8 +10290,8 @@
       </c>
       <c r="N61" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor
+then: At Q11, choose “0”, then submit.</t>
         </is>
       </c>
       <c r="O61" s="6" t="inlineStr">
@@ -10304,17 +10306,17 @@
       </c>
       <c r="Q61" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q11, choose “0”, then submit.</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S61" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T61" s="6" t="inlineStr">
@@ -10334,8 +10336,7 @@
       </c>
       <c r="W61" s="6" t="inlineStr">
         <is>
-          <t>1. Q11 is on screen
-2. the next question shown is Q12</t>
+          <t>1. Q11's wording includes: Provider A</t>
         </is>
       </c>
       <c r="X61" s="6" t="inlineStr">
@@ -10370,7 +10371,7 @@
       </c>
       <c r="AD61" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE61" s="6" t="inlineStr">
@@ -10385,7 +10386,7 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>Q12</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
@@ -10400,12 +10401,12 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
@@ -10415,27 +10416,27 @@
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>Q11 blocks a blank answer</t>
+          <t>Q12 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>Prove Q11 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove that answering Q12 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q11.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q12.</t>
         </is>
       </c>
       <c r="M62" s="6" t="inlineStr">
@@ -10445,33 +10446,33 @@
       </c>
       <c r="N62" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor
-then: At Q11, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O62" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q11 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q11 is the one the claim turns on.</t>
+          <t>Every answer before Q12 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q12 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q62" s="6" t="inlineStr">
         <is>
-          <t>At Q11, select nothing at all, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11  (refused at Q11; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S62" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T62" s="6" t="inlineStr">
@@ -10481,23 +10482,23 @@
       </c>
       <c r="U62" s="6" t="inlineStr">
         <is>
-          <t>Q12, Q13, D1, D2, Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V62" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W62" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q11</t>
+          <t>1. Q12 is on screen
+2. the next question shown is Q13</t>
         </is>
       </c>
       <c r="X62" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y62" s="6" t="inlineStr">
@@ -10507,7 +10508,7 @@
       </c>
       <c r="Z62" s="6" t="inlineStr">
         <is>
-          <t>Q11 | How likely are you to recommend the provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
+          <t>Q12 | How likely are you to continue using the provider? | single | Definitely not; Probably not; Unsure; Probably; Definitely | Always show</t>
         </is>
       </c>
       <c r="AA62" s="6" t="inlineStr">
@@ -10527,7 +10528,7 @@
       </c>
       <c r="AD62" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE62" s="6" t="inlineStr">
@@ -10542,7 +10543,7 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>Q12</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -10557,12 +10558,12 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
@@ -10572,17 +10573,17 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Q11 quotes the answer given at Q1</t>
+          <t>Q12 blocks a blank answer</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>Prove Q11's wording is built from the answer given at Q1, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove Q12 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
@@ -10592,7 +10593,7 @@
       </c>
       <c r="L63" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q11.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q12.</t>
         </is>
       </c>
       <c r="M63" s="6" t="inlineStr">
@@ -10602,33 +10603,33 @@
       </c>
       <c r="N63" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor
-then: At Q11, choose “0”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0
+then: At Q12, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O63" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q11 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q11 is the one the claim turns on.</t>
+          <t>Every answer before Q12 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q12 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q63" s="6" t="inlineStr">
         <is>
-          <t>At Q11, choose “0”, then submit.</t>
+          <t>At Q12, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12  (refused at Q12; respondent stays put)</t>
         </is>
       </c>
       <c r="S63" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12</t>
         </is>
       </c>
       <c r="T63" s="6" t="inlineStr">
@@ -10638,22 +10639,23 @@
       </c>
       <c r="U63" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V63" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W63" s="6" t="inlineStr">
         <is>
-          <t>1. Q11's wording includes: Provider A</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q12</t>
         </is>
       </c>
       <c r="X63" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y63" s="6" t="inlineStr">
@@ -10663,7 +10665,7 @@
       </c>
       <c r="Z63" s="6" t="inlineStr">
         <is>
-          <t>Q11 | How likely are you to recommend the provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
+          <t>Q12 | How likely are you to continue using the provider? | single | Definitely not; Probably not; Unsure; Probably; Definitely | Always show</t>
         </is>
       </c>
       <c r="AA63" s="6" t="inlineStr">
@@ -10683,7 +10685,7 @@
       </c>
       <c r="AD63" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE63" s="6" t="inlineStr">
@@ -10713,7 +10715,7 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>3. Dependency / Piping</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -10728,22 +10730,22 @@
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>Q12 accepts a normal answer and the survey moves on</t>
+          <t>Q12 quotes the answer given at Q1</t>
         </is>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q12 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q12's wording is built from the answer given at Q1, so the respondent is only asked about what they actually chose.</t>
         </is>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
         </is>
       </c>
       <c r="K64" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L64" s="6" t="inlineStr">
@@ -10758,8 +10760,8 @@
       </c>
       <c r="N64" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0
+then: At Q12, choose “Definitely not”, then submit.</t>
         </is>
       </c>
       <c r="O64" s="6" t="inlineStr">
@@ -10774,17 +10776,17 @@
       </c>
       <c r="Q64" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q12, choose “Definitely not”, then submit.</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S64" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T64" s="6" t="inlineStr">
@@ -10804,8 +10806,7 @@
       </c>
       <c r="W64" s="6" t="inlineStr">
         <is>
-          <t>1. Q12 is on screen
-2. the next question shown is Q13</t>
+          <t>1. Q12's wording includes: Provider A</t>
         </is>
       </c>
       <c r="X64" s="6" t="inlineStr">
@@ -10840,7 +10841,7 @@
       </c>
       <c r="AD64" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE64" s="6" t="inlineStr">
@@ -10855,7 +10856,7 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Q12</t>
+          <t>Q13</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
@@ -10870,12 +10871,12 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
@@ -10885,27 +10886,27 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Q12 blocks a blank answer</t>
+          <t>Q13 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>Prove Q12 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove that answering Q13 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q12.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q13.</t>
         </is>
       </c>
       <c r="M65" s="6" t="inlineStr">
@@ -10915,33 +10916,33 @@
       </c>
       <c r="N65" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0
-then: At Q12, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O65" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q12 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q12 is the one the claim turns on.</t>
+          <t>Every answer before Q13 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q13 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q65" s="6" t="inlineStr">
         <is>
-          <t>At Q12, select nothing at all, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12  (refused at Q12; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S65" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T65" s="6" t="inlineStr">
@@ -10951,23 +10952,23 @@
       </c>
       <c r="U65" s="6" t="inlineStr">
         <is>
-          <t>Q13, D1, D2, Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V65" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W65" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q12</t>
+          <t>1. Q13 is on screen
+2. the next question shown is DT2</t>
         </is>
       </c>
       <c r="X65" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y65" s="6" t="inlineStr">
@@ -10977,7 +10978,7 @@
       </c>
       <c r="Z65" s="6" t="inlineStr">
         <is>
-          <t>Q12 | How likely are you to continue using the provider? | single | Definitely not; Probably not; Unsure; Probably; Definitely | Always show</t>
+          <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
         </is>
       </c>
       <c r="AA65" s="6" t="inlineStr">
@@ -10997,7 +10998,7 @@
       </c>
       <c r="AD65" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE65" s="6" t="inlineStr">
@@ -11012,7 +11013,7 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Q12</t>
+          <t>Q13</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
@@ -11027,12 +11028,12 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
@@ -11042,17 +11043,17 @@
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>Q12 quotes the answer given at Q1</t>
+          <t>Q13 blocks a blank answer</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>Prove Q12's wording is built from the answer given at Q1, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove Q13 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr">
@@ -11062,7 +11063,7 @@
       </c>
       <c r="L66" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q12.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q13.</t>
         </is>
       </c>
       <c r="M66" s="6" t="inlineStr">
@@ -11072,33 +11073,33 @@
       </c>
       <c r="N66" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0
-then: At Q12, choose “Definitely not”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not
+then: At Q13, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O66" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P66" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q12 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q12 is the one the claim turns on.</t>
+          <t>Every answer before Q13 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q13 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q66" s="6" t="inlineStr">
         <is>
-          <t>At Q12, choose “Definitely not”, then submit.</t>
+          <t>At Q13, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13  (refused at Q13; respondent stays put)</t>
         </is>
       </c>
       <c r="S66" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13</t>
         </is>
       </c>
       <c r="T66" s="6" t="inlineStr">
@@ -11108,22 +11109,23 @@
       </c>
       <c r="U66" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V66" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W66" s="6" t="inlineStr">
         <is>
-          <t>1. Q12's wording includes: Provider A</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q13</t>
         </is>
       </c>
       <c r="X66" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y66" s="6" t="inlineStr">
@@ -11133,7 +11135,7 @@
       </c>
       <c r="Z66" s="6" t="inlineStr">
         <is>
-          <t>Q12 | How likely are you to continue using the provider? | single | Definitely not; Probably not; Unsure; Probably; Definitely | Always show</t>
+          <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
         </is>
       </c>
       <c r="AA66" s="6" t="inlineStr">
@@ -11153,7 +11155,7 @@
       </c>
       <c r="AD66" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE66" s="6" t="inlineStr">
@@ -11183,12 +11185,12 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>4. Randomization</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8. Implementation Conformance</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
@@ -11198,22 +11200,22 @@
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>Q13 accepts a normal answer and the survey moves on</t>
+          <t>Q13 shuffles without losing an option</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q13 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q13 still presents all 5 of its options when shuffled, with none dropped and none repeated.</t>
         </is>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>Without a genuine shuffle the option order biases the answers, and without the recorded order the answers cannot be corrected later.</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr">
@@ -11228,8 +11230,8 @@
       </c>
       <c r="N67" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not
+then: At Q13, choose “Lower cost”, then submit.</t>
         </is>
       </c>
       <c r="O67" s="6" t="inlineStr">
@@ -11244,17 +11246,17 @@
       </c>
       <c r="Q67" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q13, choose “Lower cost”, then submit.</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S67" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T67" s="6" t="inlineStr">
@@ -11274,8 +11276,8 @@
       </c>
       <c r="W67" s="6" t="inlineStr">
         <is>
-          <t>1. Q13 is on screen
-2. the next question shown is D1</t>
+          <t>1. Q13 shows exactly 5 options, none missing or repeated
+2. the options shown at Q13 are exactly: Better staff support, Clearer information, Faster service, Improved digital experience, Lower cost</t>
         </is>
       </c>
       <c r="X67" s="6" t="inlineStr">
@@ -11310,7 +11312,7 @@
       </c>
       <c r="AD67" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the order varies, only that nothing was lost or repeated. Order is a separate test needing several runs.</t>
         </is>
       </c>
       <c r="AE67" s="6" t="inlineStr">
@@ -11330,22 +11332,22 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>TC-FT60</t>
+          <t>TC-ST03</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>FOCUSED</t>
+          <t>STATEFUL</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>4. Randomization</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>8. Implementation Conformance</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
@@ -11355,17 +11357,17 @@
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>Q13 blocks a blank answer</t>
+          <t>Q13 genuinely varies its option order</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>Prove Q13 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove Q13 is genuinely shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on.</t>
         </is>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Without a genuine shuffle the option order biases the answers, and without the recorded order the answers cannot be corrected later.</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr">
@@ -11375,7 +11377,7 @@
       </c>
       <c r="L68" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q13.</t>
+          <t>Run this same path 5 times and compare the recorded option order between runs.</t>
         </is>
       </c>
       <c r="M68" s="6" t="inlineStr">
@@ -11386,12 +11388,12 @@
       <c r="N68" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not
-then: At Q13, select nothing at all, then submit.</t>
+then: At Q13, choose “Lower cost”, then submit.</t>
         </is>
       </c>
       <c r="O68" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P68" s="6" t="inlineStr">
@@ -11401,17 +11403,17 @@
       </c>
       <c r="Q68" s="6" t="inlineStr">
         <is>
-          <t>At Q13, select nothing at all, then submit.</t>
+          <t>At Q13, choose “Lower cost”, then submit.</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13  (refused at Q13; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S68" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T68" s="6" t="inlineStr">
@@ -11421,23 +11423,22 @@
       </c>
       <c r="U68" s="6" t="inlineStr">
         <is>
-          <t>D1, D2, Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V68" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W68" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q13</t>
+          <t>1. the option order at Q13 is NOT identical on every run</t>
         </is>
       </c>
       <c r="X68" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y68" s="6" t="inlineStr">
@@ -11467,7 +11468,7 @@
       </c>
       <c r="AD68" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove any particular order is correct, only that the order is not fixed.</t>
         </is>
       </c>
       <c r="AE68" s="6" t="inlineStr">
@@ -11482,12 +11483,12 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>DT2</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>TC-FT61</t>
+          <t>TC-FT60</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -11497,12 +11498,12 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>4. Randomization</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>8. Implementation Conformance</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
@@ -11512,27 +11513,27 @@
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>Q13 shuffles without losing an option</t>
+          <t>DT2 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>Prove Q13 still presents all 5 of its options when shuffled, with none dropped and none repeated.</t>
+          <t>Prove that answering DT2 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>Without a genuine shuffle the option order biases the answers, and without the recorded order the answers cannot be corrected later.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q13.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as DT2.</t>
         </is>
       </c>
       <c r="M69" s="6" t="inlineStr">
@@ -11542,8 +11543,8 @@
       </c>
       <c r="N69" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not
-then: At Q13, choose “Lower cost”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O69" s="6" t="inlineStr">
@@ -11553,22 +11554,22 @@
       </c>
       <c r="P69" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q13 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q13 is the one the claim turns on.</t>
+          <t>Every answer before DT2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at DT2 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q69" s="6" t="inlineStr">
         <is>
-          <t>At Q13, choose “Lower cost”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S69" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T69" s="6" t="inlineStr">
@@ -11588,8 +11589,7 @@
       </c>
       <c r="W69" s="6" t="inlineStr">
         <is>
-          <t>1. Q13 shows exactly 5 options, none missing or repeated
-2. the options shown at Q13 are exactly: Better staff support, Clearer information, Faster service, Improved digital experience, Lower cost</t>
+          <t>1. the next question shown is D1</t>
         </is>
       </c>
       <c r="X69" s="6" t="inlineStr">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="Z69" s="6" t="inlineStr">
         <is>
-          <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
+          <t>DT2 | You're almost done! Thank you for your answers. Just a few last questions about you to finish up. | text display | — | Always show</t>
         </is>
       </c>
       <c r="AA69" s="6" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="AD69" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the order varies, only that nothing was lost or repeated. Order is a separate test needing several runs.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE69" s="6" t="inlineStr">
@@ -11639,27 +11639,27 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>TC-ST03</t>
+          <t>TC-FT61</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>STATEFUL</t>
+          <t>FOCUSED</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>4. Randomization</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>8. Implementation Conformance</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
@@ -11669,27 +11669,27 @@
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>Q13 genuinely varies its option order</t>
+          <t>D1 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>Prove Q13 is genuinely shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on.</t>
+          <t>Prove that answering D1 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>Without a genuine shuffle the option order biases the answers, and without the recorded order the answers cannot be corrected later.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr">
         <is>
-          <t>Run this same path 5 times and compare the recorded option order between runs.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as D1.</t>
         </is>
       </c>
       <c r="M70" s="6" t="inlineStr">
@@ -11699,8 +11699,8 @@
       </c>
       <c r="N70" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not
-then: At Q13, choose “Lower cost”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O70" s="6" t="inlineStr">
@@ -11710,22 +11710,22 @@
       </c>
       <c r="P70" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q13 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q13 is the one the claim turns on.</t>
+          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q70" s="6" t="inlineStr">
         <is>
-          <t>At Q13, choose “Lower cost”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S70" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T70" s="6" t="inlineStr">
@@ -11745,7 +11745,8 @@
       </c>
       <c r="W70" s="6" t="inlineStr">
         <is>
-          <t>1. the option order at Q13 is NOT identical on every run</t>
+          <t>1. D1 is on screen
+2. the next question shown is D2</t>
         </is>
       </c>
       <c r="X70" s="6" t="inlineStr">
@@ -11760,7 +11761,7 @@
       </c>
       <c r="Z70" s="6" t="inlineStr">
         <is>
-          <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
+          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
       <c r="AA70" s="6" t="inlineStr">
@@ -11780,7 +11781,7 @@
       </c>
       <c r="AD70" s="6" t="inlineStr">
         <is>
-          <t>It does not prove any particular order is correct, only that the order is not fixed.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE70" s="6" t="inlineStr">
@@ -11810,12 +11811,12 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
@@ -11825,22 +11826,22 @@
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>D1 accepts a normal answer and the survey moves on</t>
+          <t>D1 blocks a blank answer</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering D1 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove D1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr">
@@ -11855,13 +11856,13 @@
       </c>
       <c r="N71" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
+then: At D1, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O71" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P71" s="6" t="inlineStr">
@@ -11871,17 +11872,17 @@
       </c>
       <c r="Q71" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At D1, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1  (refused at D1; respondent stays put)</t>
         </is>
       </c>
       <c r="S71" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1</t>
         </is>
       </c>
       <c r="T71" s="6" t="inlineStr">
@@ -11891,23 +11892,23 @@
       </c>
       <c r="U71" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>D2, Q14</t>
         </is>
       </c>
       <c r="V71" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W71" s="6" t="inlineStr">
         <is>
-          <t>1. D1 is on screen
-2. the next question shown is D2</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against D1</t>
         </is>
       </c>
       <c r="X71" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y71" s="6" t="inlineStr">
@@ -11937,7 +11938,7 @@
       </c>
       <c r="AD71" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE71" s="6" t="inlineStr">
@@ -11967,42 +11968,42 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>5. Quota / Stateful</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>6. Termination / Disposition</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>D1 blocks a blank answer</t>
+          <t>QUOTA_REGION admits a respondent while D1-O1 is open</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>Prove D1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove QUOTA_REGION lets a 'North' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L72" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as D1.</t>
+          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
         </is>
       </c>
       <c r="M72" s="6" t="inlineStr">
@@ -12013,12 +12014,12 @@
       <c r="N72" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
-then: At D1, select nothing at all, then submit.</t>
+then: At D1, choose “North”, then submit.</t>
         </is>
       </c>
       <c r="O72" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P72" s="6" t="inlineStr">
@@ -12028,43 +12029,42 @@
       </c>
       <c r="Q72" s="6" t="inlineStr">
         <is>
-          <t>At D1, select nothing at all, then submit.</t>
+          <t>At D1, choose “North”, then submit.</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1  (refused at D1; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S72" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T72" s="6" t="inlineStr">
         <is>
-          <t>Q8, Q9, Q10</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U72" s="6" t="inlineStr">
         <is>
-          <t>D2, Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V72" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W72" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against D1</t>
+          <t>1. the respondent is allowed to continue</t>
         </is>
       </c>
       <c r="X72" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y72" s="6" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="AD72" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
         </is>
       </c>
       <c r="AE72" s="6" t="inlineStr">
@@ -12139,12 +12139,12 @@
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_REGION admits a respondent while D1-O1 is open</t>
+          <t>QUOTA_REGION admits a respondent while D1-O2 is open</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_REGION lets a 'North' respondent through while that group is below its target.</t>
+          <t>Prove QUOTA_REGION lets a 'South' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J73" s="6" t="inlineStr">
@@ -12170,7 +12170,7 @@
       <c r="N73" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
-then: At D1, choose “North”, then submit.</t>
+then: At D1, choose “South”, then submit.</t>
         </is>
       </c>
       <c r="O73" s="6" t="inlineStr">
@@ -12185,17 +12185,17 @@
       </c>
       <c r="Q73" s="6" t="inlineStr">
         <is>
-          <t>At D1, choose “North”, then submit.</t>
+          <t>At D1, choose “South”, then submit.</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S73" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T73" s="6" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_REGION admits a respondent while D1-O2 is open</t>
+          <t>QUOTA_REGION admits a respondent while D1-O3 is open</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_REGION lets a 'South' respondent through while that group is below its target.</t>
+          <t>Prove QUOTA_REGION lets a 'East' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J74" s="6" t="inlineStr">
@@ -12326,7 +12326,7 @@
       <c r="N74" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
-then: At D1, choose “South”, then submit.</t>
+then: At D1, choose “East”, then submit.</t>
         </is>
       </c>
       <c r="O74" s="6" t="inlineStr">
@@ -12341,17 +12341,17 @@
       </c>
       <c r="Q74" s="6" t="inlineStr">
         <is>
-          <t>At D1, choose “South”, then submit.</t>
+          <t>At D1, choose “East”, then submit.</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S74" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T74" s="6" t="inlineStr">
@@ -12451,12 +12451,12 @@
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_REGION admits a respondent while D1-O3 is open</t>
+          <t>QUOTA_REGION admits a respondent while D1-O4 is open</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_REGION lets a 'East' respondent through while that group is below its target.</t>
+          <t>Prove QUOTA_REGION lets a 'West' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J75" s="6" t="inlineStr">
@@ -12482,7 +12482,7 @@
       <c r="N75" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
-then: At D1, choose “East”, then submit.</t>
+then: At D1, choose “West”, then submit.</t>
         </is>
       </c>
       <c r="O75" s="6" t="inlineStr">
@@ -12497,17 +12497,17 @@
       </c>
       <c r="Q75" s="6" t="inlineStr">
         <is>
-          <t>At D1, choose “East”, then submit.</t>
+          <t>At D1, choose “West”, then submit.</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S75" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T75" s="6" t="inlineStr">
@@ -12607,12 +12607,12 @@
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_REGION admits a respondent while D1-O4 is open</t>
+          <t>QUOTA_REGION admits a respondent while D1-O5 is open</t>
         </is>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_REGION lets a 'West' respondent through while that group is below its target.</t>
+          <t>Prove QUOTA_REGION lets a 'Central' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J76" s="6" t="inlineStr">
@@ -12638,7 +12638,7 @@
       <c r="N76" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
-then: At D1, choose “West”, then submit.</t>
+then: At D1, choose “Central”, then submit.</t>
         </is>
       </c>
       <c r="O76" s="6" t="inlineStr">
@@ -12653,17 +12653,17 @@
       </c>
       <c r="Q76" s="6" t="inlineStr">
         <is>
-          <t>At D1, choose “West”, then submit.</t>
+          <t>At D1, choose “Central”, then submit.</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S76" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T76" s="6" t="inlineStr">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -12748,42 +12748,42 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>5. Quota / Stateful</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>6. Termination / Disposition</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_REGION admits a respondent while D1-O5 is open</t>
+          <t>D2 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_REGION lets a 'Central' respondent through while that group is below its target.</t>
+          <t>Prove that answering D2 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as D2.</t>
         </is>
       </c>
       <c r="M77" s="6" t="inlineStr">
@@ -12793,8 +12793,8 @@
       </c>
       <c r="N77" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
-then: At D1, choose “Central”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O77" s="6" t="inlineStr">
@@ -12804,34 +12804,34 @@
       </c>
       <c r="P77" s="6" t="inlineStr">
         <is>
-          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
+          <t>Every answer before D2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D2 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q77" s="6" t="inlineStr">
         <is>
-          <t>At D1, choose “Central”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R77" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S77" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T77" s="6" t="inlineStr">
         <is>
+          <t>Q8, Q9, Q10</t>
+        </is>
+      </c>
+      <c r="U77" s="6" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U77" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="V77" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
@@ -12839,7 +12839,8 @@
       </c>
       <c r="W77" s="6" t="inlineStr">
         <is>
-          <t>1. the respondent is allowed to continue</t>
+          <t>1. D2 is on screen
+2. the next question shown is Q14</t>
         </is>
       </c>
       <c r="X77" s="6" t="inlineStr">
@@ -12854,7 +12855,7 @@
       </c>
       <c r="Z77" s="6" t="inlineStr">
         <is>
-          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
+          <t>D2 | Which age group describes you? | single | 18-24; 25-34; 35-44; 45-54; 55+ | Always show</t>
         </is>
       </c>
       <c r="AA77" s="6" t="inlineStr">
@@ -12874,7 +12875,7 @@
       </c>
       <c r="AD77" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE77" s="6" t="inlineStr">
@@ -12904,12 +12905,12 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
@@ -12919,22 +12920,22 @@
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>D2 accepts a normal answer and the survey moves on</t>
+          <t>D2 blocks a blank answer</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering D2 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove D2 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K78" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L78" s="6" t="inlineStr">
@@ -12949,13 +12950,13 @@
       </c>
       <c r="N78" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North
+then: At D2, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O78" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P78" s="6" t="inlineStr">
@@ -12965,17 +12966,17 @@
       </c>
       <c r="Q78" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At D2, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R78" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2  (refused at D2; respondent stays put)</t>
         </is>
       </c>
       <c r="S78" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2</t>
         </is>
       </c>
       <c r="T78" s="6" t="inlineStr">
@@ -12985,23 +12986,23 @@
       </c>
       <c r="U78" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q14</t>
         </is>
       </c>
       <c r="V78" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W78" s="6" t="inlineStr">
         <is>
-          <t>1. D2 is on screen
-2. the next question shown is Q14</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against D2</t>
         </is>
       </c>
       <c r="X78" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y78" s="6" t="inlineStr">
@@ -13031,7 +13032,7 @@
       </c>
       <c r="AD78" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE78" s="6" t="inlineStr">
@@ -13046,7 +13047,7 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>Q14</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -13061,12 +13062,12 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
@@ -13076,27 +13077,27 @@
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>D2 blocks a blank answer</t>
+          <t>Q14 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>Prove D2 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove that answering Q14 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as D2.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
         </is>
       </c>
       <c r="M79" s="6" t="inlineStr">
@@ -13106,33 +13107,33 @@
       </c>
       <c r="N79" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North
-then: At D2, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O79" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P79" s="6" t="inlineStr">
         <is>
-          <t>Every answer before D2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D2 is the one the claim turns on.</t>
+          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q79" s="6" t="inlineStr">
         <is>
-          <t>At D2, select nothing at all, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R79" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2  (refused at D2; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S79" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T79" s="6" t="inlineStr">
@@ -13142,23 +13143,23 @@
       </c>
       <c r="U79" s="6" t="inlineStr">
         <is>
-          <t>Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V79" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W79" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against D2</t>
+          <t>1. Q14 is on screen
+2. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
       <c r="X79" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y79" s="6" t="inlineStr">
@@ -13168,7 +13169,8 @@
       </c>
       <c r="Z79" s="6" t="inlineStr">
         <is>
-          <t>D2 | Which age group describes you? | single | 18-24; 25-34; 35-44; 45-54; 55+ | Always show</t>
+          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
+Optional</t>
         </is>
       </c>
       <c r="AA79" s="6" t="inlineStr">
@@ -13188,7 +13190,7 @@
       </c>
       <c r="AD79" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE79" s="6" t="inlineStr">
@@ -13218,7 +13220,7 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
@@ -13233,17 +13235,17 @@
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>Q14 accepts a normal answer and the survey moves on</t>
+          <t>Q14 accepts a valid answer</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q14 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q14 accepts an answer that obeys its stated rule. The rule is: at most 750 characters</t>
         </is>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K80" s="6" t="inlineStr">
@@ -13264,12 +13266,12 @@
       <c r="N80" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+then: At Q14, type “x”, then submit.</t>
         </is>
       </c>
       <c r="O80" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>VALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P80" s="6" t="inlineStr">
@@ -13279,17 +13281,17 @@
       </c>
       <c r="Q80" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q14, type “x”, then submit.</t>
         </is>
       </c>
       <c r="R80" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S80" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T80" s="6" t="inlineStr">
@@ -13309,8 +13311,7 @@
       </c>
       <c r="W80" s="6" t="inlineStr">
         <is>
-          <t>1. Q14 is on screen
-2. the respondent reaches the normal thank-you page</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X80" s="6" t="inlineStr">
@@ -13346,7 +13347,7 @@
       </c>
       <c r="AD80" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE80" s="6" t="inlineStr">
@@ -13381,7 +13382,7 @@
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -13391,12 +13392,12 @@
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>Q14 accepts a valid answer</t>
+          <t>Q14 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>Prove Q14 accepts an answer that obeys its stated rule. The rule is: at most 750 characters</t>
+          <t>Prove Q14 refuses an answer that breaks its stated rule. The rule is: at most 750 characters</t>
         </is>
       </c>
       <c r="J81" s="6" t="inlineStr">
@@ -13422,12 +13423,12 @@
       <c r="N81" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: At Q14, type “x”, then submit.</t>
+then: At Q14, type a 751-character answer, then submit.</t>
         </is>
       </c>
       <c r="O81" s="6" t="inlineStr">
         <is>
-          <t>VALID_BOUNDARY</t>
+          <t>INVALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P81" s="6" t="inlineStr">
@@ -13437,17 +13438,17 @@
       </c>
       <c r="Q81" s="6" t="inlineStr">
         <is>
-          <t>At Q14, type “x”, then submit.</t>
+          <t>At Q14, type a 751-character answer, then submit.</t>
         </is>
       </c>
       <c r="R81" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14  (refused at Q14; respondent stays put)</t>
         </is>
       </c>
       <c r="S81" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T81" s="6" t="inlineStr">
@@ -13462,17 +13463,18 @@
       </c>
       <c r="V81" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W81" s="6" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q14</t>
         </is>
       </c>
       <c r="X81" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y81" s="6" t="inlineStr">
@@ -13538,7 +13540,7 @@
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
@@ -13548,22 +13550,22 @@
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>Q14 rejects an invalid answer</t>
+          <t>Q14 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
-          <t>Prove Q14 refuses an answer that breaks its stated rule. The rule is: at most 750 characters</t>
+          <t>Prove Q14 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr">
@@ -13579,12 +13581,12 @@
       <c r="N82" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: At Q14, type a 751-character answer, then submit.</t>
+then: At Q14, type nothing, then submit.</t>
         </is>
       </c>
       <c r="O82" s="6" t="inlineStr">
         <is>
-          <t>INVALID_BOUNDARY</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P82" s="6" t="inlineStr">
@@ -13594,17 +13596,17 @@
       </c>
       <c r="Q82" s="6" t="inlineStr">
         <is>
-          <t>At Q14, type a 751-character answer, then submit.</t>
+          <t>At Q14, type nothing, then submit.</t>
         </is>
       </c>
       <c r="R82" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14  (refused at Q14; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S82" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T82" s="6" t="inlineStr">
@@ -13619,18 +13621,17 @@
       </c>
       <c r="V82" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W82" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q14</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X82" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y82" s="6" t="inlineStr">
@@ -13661,7 +13662,7 @@
       </c>
       <c r="AD82" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE82" s="6" t="inlineStr">
@@ -13706,22 +13707,22 @@
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>Q14 allows a blank answer, being optional</t>
+          <t>Q14 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>Prove Q14 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
+          <t>Prove Q14 refuses an answer that breaks its stated rule. The rule is: at most 750 characters</t>
         </is>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr">
@@ -13737,12 +13738,12 @@
       <c r="N83" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: At Q14, type nothing, then submit.</t>
+then: At Q14, type a 750-character answer, then submit.</t>
         </is>
       </c>
       <c r="O83" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P83" s="6" t="inlineStr">
@@ -13752,17 +13753,17 @@
       </c>
       <c r="Q83" s="6" t="inlineStr">
         <is>
-          <t>At Q14, type nothing, then submit.</t>
+          <t>At Q14, type a 750-character answer, then submit.</t>
         </is>
       </c>
       <c r="R83" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S83" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T83" s="6" t="inlineStr">
@@ -13818,7 +13819,7 @@
       </c>
       <c r="AD83" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE83" s="6" t="inlineStr">
@@ -13894,7 +13895,7 @@
       <c r="N84" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: At Q14, type a 750-character answer, then submit.</t>
+then: At Q14, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="O84" s="6" t="inlineStr">
@@ -13909,17 +13910,17 @@
       </c>
       <c r="Q84" s="6" t="inlineStr">
         <is>
-          <t>At Q14, type a 750-character answer, then submit.</t>
+          <t>At Q14, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="R84" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S84" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T84" s="6" t="inlineStr">
@@ -14020,22 +14021,22 @@
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>Q14 rejects an invalid answer</t>
+          <t>Q14 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
-          <t>Prove Q14 refuses an answer that breaks its stated rule. The rule is: at most 750 characters</t>
+          <t>Prove Q14 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr">
@@ -14051,7 +14052,7 @@
       <c r="N85" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: At Q14, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
+then: At Q14, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="O85" s="6" t="inlineStr">
@@ -14066,17 +14067,17 @@
       </c>
       <c r="Q85" s="6" t="inlineStr">
         <is>
-          <t>At Q14, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
+          <t>At Q14, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="R85" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S85" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T85" s="6" t="inlineStr">
@@ -14132,12 +14133,12 @@
       </c>
       <c r="AD85" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE85" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
+          <t>Leans on an unconfirmed reading: multi_equality, whitespace_is_an_answer</t>
         </is>
       </c>
     </row>
@@ -14147,27 +14148,27 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Q14</t>
+          <t>whole survey</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>TC-FT77</t>
+          <t>TC-RT03</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>FOCUSED</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>6. Termination / Disposition</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
@@ -14177,27 +14178,27 @@
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>Q14 allows a blank answer, being optional</t>
+          <t>End-to-end journey: COMPLETE by way of routing</t>
         </is>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>Prove Q14 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
+          <t>Prove that a respondent answering as listed is shown exactly this sequence of questions, in this order, and ends at COMPLETE by way of the routing, checked at ?. Condition: . They should then see: “Thank you. Your response has been recorded.”</t>
         </is>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Screening someone out incorrectly loses a valid respondent and the money spent recruiting them. Failing to screen someone out puts the wrong person in the sample.</t>
         </is>
       </c>
       <c r="K86" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L86" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as the end.</t>
         </is>
       </c>
       <c r="M86" s="6" t="inlineStr">
@@ -14206,249 +14207,92 @@
         </is>
       </c>
       <c r="N86" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: At Q14, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="O86" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P86" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q86" s="6" t="inlineStr">
-        <is>
-          <t>At Q14, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="R86" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
-        </is>
-      </c>
-      <c r="S86" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
-        </is>
-      </c>
-      <c r="T86" s="6" t="inlineStr">
-        <is>
-          <t>Q8, Q9, Q10</t>
-        </is>
-      </c>
-      <c r="U86" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V86" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W86" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
-        </is>
-      </c>
-      <c r="X86" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y86" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z86" s="6" t="inlineStr">
-        <is>
-          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA86" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB86" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC86" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD86" s="6" t="inlineStr">
-        <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
-        </is>
-      </c>
-      <c r="AE86" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: multi_equality, whitespace_is_an_answer</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="B87" s="9" t="inlineStr">
-        <is>
-          <t>whole survey</t>
-        </is>
-      </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>TC-RT03</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>ROUTE</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>6. Termination / Disposition</t>
-        </is>
-      </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>1. Flow / Routing</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H87" s="6" t="inlineStr">
-        <is>
-          <t>End-to-end journey: COMPLETE by way of routing</t>
-        </is>
-      </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>Prove that a respondent answering as listed is shown exactly this sequence of questions, in this order, and ends at COMPLETE by way of the routing, checked at ?. Condition: . They should then see: “Thank you. Your response has been recorded.”</t>
-        </is>
-      </c>
-      <c r="J87" s="6" t="inlineStr">
-        <is>
-          <t>Screening someone out incorrectly loses a valid respondent and the money spent recruiting them. Failing to screen someone out puts the wrong person in the sample.</t>
-        </is>
-      </c>
-      <c r="K87" s="6" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="L87" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as the end.</t>
-        </is>
-      </c>
-      <c r="M87" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N87" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
 then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="O87" s="6" t="inlineStr">
+      <c r="O86" s="6" t="inlineStr">
         <is>
           <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
-      <c r="P87" s="6" t="inlineStr">
+      <c r="P86" s="6" t="inlineStr">
         <is>
           <t>Chosen to walk the whole survey without triggering a screen-out.</t>
         </is>
       </c>
-      <c r="Q87" s="6" t="inlineStr">
+      <c r="Q86" s="6" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="R87" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; D1 -&gt; D2 -&gt; Q14</t>
-        </is>
-      </c>
-      <c r="S87" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, S3, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, D1, D2, Q14</t>
-        </is>
-      </c>
-      <c r="T87" s="6" t="inlineStr">
+      <c r="R86" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+        </is>
+      </c>
+      <c r="S86" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+        </is>
+      </c>
+      <c r="T86" s="6" t="inlineStr">
         <is>
           <t>Q8, Q9, Q10</t>
         </is>
       </c>
-      <c r="U87" s="6" t="inlineStr">
+      <c r="U86" s="6" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="V87" s="6" t="inlineStr">
+      <c r="V86" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
-      <c r="W87" s="6" t="inlineStr">
+      <c r="W86" s="6" t="inlineStr">
         <is>
           <t>1. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
-      <c r="X87" s="6" t="inlineStr">
+      <c r="X86" s="6" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="Y87" s="6" t="inlineStr">
+      <c r="Y86" s="6" t="inlineStr">
         <is>
           <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
         </is>
       </c>
-      <c r="Z87" s="6" t="inlineStr">
+      <c r="Z86" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AA87" s="6" t="inlineStr">
+      <c r="AA86" s="6" t="inlineStr">
         <is>
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB87" s="10" t="inlineStr">
+      <c r="AB86" s="10" t="inlineStr">
         <is>
           <t>PROVISIONAL</t>
         </is>
       </c>
-      <c r="AC87" s="8" t="inlineStr">
+      <c r="AC86" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AD87" s="6" t="inlineStr">
+      <c r="AD86" s="6" t="inlineStr">
         <is>
           <t>It does not prove any validation rule: every answer on this path is deliberately valid. It does not prove randomization or quota behaviour.</t>
         </is>
       </c>
-      <c r="AE87" s="6" t="inlineStr">
+      <c r="AE86" s="6" t="inlineStr">
         <is>
           <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>

--- a/out/M01_mobile_network_experience/agent3/agent3_test_cases_with_paths.xlsx
+++ b/out/M01_mobile_network_experience/agent3/agent3_test_cases_with_paths.xlsx
@@ -906,7 +906,7 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>11 test(s): TC-FT45, TC-FT46, TC-FT47, TC-FT48, TC-FT49, TC-FT50 ...</t>
+          <t>9 test(s): TC-FT43, TC-FT44, TC-FT45, TC-FT46, TC-FT57, TC-FT58 ...</t>
         </is>
       </c>
       <c r="Q7" s="8" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>51 test(s): TC-FT05, TC-FT06, TC-FT07, TC-FT08, TC-FT09, TC-FT10 ...</t>
+          <t>49 test(s): TC-FT05, TC-FT06, TC-FT07, TC-FT08, TC-FT09, TC-FT10 ...</t>
         </is>
       </c>
       <c r="Q8" s="8" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>14 test(s): TC-FT31, TC-FT32, TC-FT33, TC-FT34, TC-FT35, TC-FT36 ...</t>
+          <t>12 test(s): TC-FT31, TC-FT32, TC-FT33, TC-FT34, TC-FT35, TC-FT36 ...</t>
         </is>
       </c>
       <c r="Q10" s="8" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE86"/>
+  <dimension ref="A1:AE80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -8686,32 +8686,32 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Q9 quotes the answer given at Q7</t>
+          <t>Q10 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>Prove Q9's wording is built from the answer given at Q7, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove that answering Q10 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr">
         <is>
-          <t>Travel path P06 (Completing respondent — Q7=Support delay; Q9=No) as far as Q9.</t>
+          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as Q10.</t>
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr">
@@ -8721,8 +8721,8 @@
       </c>
       <c r="N51" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls
-then: At Q9, choose “Yes, fully”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O51" s="6" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q9 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q9 is the one the claim turns on.</t>
+          <t>Every answer before Q10 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q10 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
-          <t>At Q9, choose “Yes, fully”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="T51" s="6" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U51" s="6" t="inlineStr">
@@ -8767,7 +8767,8 @@
       </c>
       <c r="W51" s="6" t="inlineStr">
         <is>
-          <t>1. Q9's wording includes: Dropped calls</t>
+          <t>1. Q10 is on screen
+2. the next question shown is Q11</t>
         </is>
       </c>
       <c r="X51" s="6" t="inlineStr">
@@ -8782,12 +8783,12 @@
       </c>
       <c r="Z51" s="6" t="inlineStr">
         <is>
-          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
+          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
       <c r="AA51" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
       <c r="AB51" s="10" t="inlineStr">
@@ -8802,7 +8803,7 @@
       </c>
       <c r="AD51" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE51" s="6" t="inlineStr">
@@ -8817,7 +8818,7 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
@@ -8832,42 +8833,42 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>9. Rule Interaction</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>Q9 is shown and reflects its dependency on Q7 at the same time</t>
+          <t>Q10 is shown when its condition is met</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>Prove Q9 is shown by its display rule and simultaneously reflects its dependency on Q7. Each mechanism can be correct alone and still disagree together.</t>
+          <t>Prove Q10 IS shown when its display rule is satisfied. The rule is: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>Individually correct rules can combine into behaviour neither one describes on its own.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L52" s="6" t="inlineStr">
         <is>
-          <t>Travel path P06 (Completing respondent — Q7=Support delay; Q9=No) as far as Q9.</t>
+          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as Q10.</t>
         </is>
       </c>
       <c r="M52" s="6" t="inlineStr">
@@ -8877,8 +8878,8 @@
       </c>
       <c r="N52" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls
-then: At Q9, choose “Yes, fully”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully
+then: At Q10, choose “Very poor”, then submit.</t>
         </is>
       </c>
       <c r="O52" s="6" t="inlineStr">
@@ -8888,12 +8889,12 @@
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q9 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q9 is the one the claim turns on.</t>
+          <t>Every answer before Q10 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q10 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
-          <t>At Q9, choose “Yes, fully”, then submit.</t>
+          <t>At Q10, choose “Very poor”, then submit.</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
@@ -8908,7 +8909,7 @@
       </c>
       <c r="T52" s="6" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U52" s="6" t="inlineStr">
@@ -8923,8 +8924,7 @@
       </c>
       <c r="W52" s="6" t="inlineStr">
         <is>
-          <t>1. Q9 is on screen
-2. Q9's wording includes: Dropped calls</t>
+          <t>1. Q10 is on screen</t>
         </is>
       </c>
       <c r="X52" s="6" t="inlineStr">
@@ -8939,12 +8939,13 @@
       </c>
       <c r="Z52" s="6" t="inlineStr">
         <is>
-          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
+          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']
+Rules exercised: R7</t>
         </is>
       </c>
       <c r="AA52" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
       <c r="AB52" s="10" t="inlineStr">
@@ -8994,7 +8995,7 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
@@ -9004,12 +9005,12 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Q10 accepts a normal answer and the survey moves on</t>
+          <t>Q10 is not shown when its condition is not met</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q10 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q10 is NOT shown when its display rule is not satisfied. The rule is: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
@@ -9034,13 +9035,13 @@
       </c>
       <c r="N53" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = No
+then: After submitting Q9, look for Q10 on the next page. Do not answer it.</t>
         </is>
       </c>
       <c r="O53" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>VALID_TYPICAL (the branch that hides the question)</t>
         </is>
       </c>
       <c r="P53" s="6" t="inlineStr">
@@ -9050,17 +9051,17 @@
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>After submitting Q9, look for Q10 on the next page. Do not answer it.</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S53" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T53" s="6" t="inlineStr">
@@ -9070,7 +9071,7 @@
       </c>
       <c r="U53" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="V53" s="6" t="inlineStr">
@@ -9080,8 +9081,8 @@
       </c>
       <c r="W53" s="6" t="inlineStr">
         <is>
-          <t>1. Q10 is on screen
-2. the next question shown is Q11</t>
+          <t>1. Q10 is NOT on screen
+2. the respondent carries on rather than being screened out or finished</t>
         </is>
       </c>
       <c r="X53" s="6" t="inlineStr">
@@ -9096,7 +9097,8 @@
       </c>
       <c r="Z53" s="6" t="inlineStr">
         <is>
-          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
+          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']
+Rules exercised: R7</t>
         </is>
       </c>
       <c r="AA53" s="6" t="inlineStr">
@@ -9116,12 +9118,12 @@
       </c>
       <c r="AD53" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove why the question was absent beyond the display rule; the check confirms the respondent was still travelling and had not been screened out. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE53" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
+          <t>Leans on an unconfirmed reading: multi_equality, rule_precedence</t>
         </is>
       </c>
     </row>
@@ -9146,12 +9148,12 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
@@ -9161,22 +9163,22 @@
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>Q10 is shown when its condition is met</t>
+          <t>Q10 blocks a blank answer</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>Prove Q10 IS shown when its display rule is satisfied. The rule is: Q9 in ['Yes, fully','Yes, partly']</t>
+          <t>Prove Q10 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L54" s="6" t="inlineStr">
@@ -9192,12 +9194,12 @@
       <c r="N54" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully
-then: At Q10, choose “Very poor”, then submit.</t>
+then: At Q10, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O54" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P54" s="6" t="inlineStr">
@@ -9207,17 +9209,17 @@
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
-          <t>At Q10, choose “Very poor”, then submit.</t>
+          <t>At Q10, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10  (refused at Q10; respondent stays put)</t>
         </is>
       </c>
       <c r="S54" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10</t>
         </is>
       </c>
       <c r="T54" s="6" t="inlineStr">
@@ -9227,22 +9229,23 @@
       </c>
       <c r="U54" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V54" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W54" s="6" t="inlineStr">
         <is>
-          <t>1. Q10 is on screen</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q10</t>
         </is>
       </c>
       <c r="X54" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y54" s="6" t="inlineStr">
@@ -9252,8 +9255,7 @@
       </c>
       <c r="Z54" s="6" t="inlineStr">
         <is>
-          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']
-Rules exercised: R7</t>
+          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
       <c r="AA54" s="6" t="inlineStr">
@@ -9273,7 +9275,7 @@
       </c>
       <c r="AD54" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE54" s="6" t="inlineStr">
@@ -9288,7 +9290,7 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Q11</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -9308,22 +9310,22 @@
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>Q10 is not shown when its condition is not met</t>
+          <t>Q11 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>Prove Q10 is NOT shown when its display rule is not satisfied. The rule is: Q9 in ['Yes, fully','Yes, partly']</t>
+          <t>Prove that answering Q11 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr">
@@ -9338,7 +9340,7 @@
       </c>
       <c r="L55" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as Q10.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q11.</t>
         </is>
       </c>
       <c r="M55" s="6" t="inlineStr">
@@ -9348,45 +9350,45 @@
       </c>
       <c r="N55" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = No
-then: After submitting Q9, look for Q10 on the next page. Do not answer it.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O55" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL (the branch that hides the question)</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q10 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q10 is the one the claim turns on.</t>
+          <t>Every answer before Q11 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q11 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
-          <t>After submitting Q9, look for Q10 on the next page. Do not answer it.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S55" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T55" s="6" t="inlineStr">
         <is>
+          <t>Q8, Q9, Q10</t>
+        </is>
+      </c>
+      <c r="U55" s="6" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U55" s="6" t="inlineStr">
-        <is>
-          <t>Q10</t>
-        </is>
-      </c>
       <c r="V55" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
@@ -9394,8 +9396,8 @@
       </c>
       <c r="W55" s="6" t="inlineStr">
         <is>
-          <t>1. Q10 is NOT on screen
-2. the respondent carries on rather than being screened out or finished</t>
+          <t>1. Q11 is on screen
+2. the next question shown is Q12</t>
         </is>
       </c>
       <c r="X55" s="6" t="inlineStr">
@@ -9410,13 +9412,12 @@
       </c>
       <c r="Z55" s="6" t="inlineStr">
         <is>
-          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']
-Rules exercised: R7</t>
+          <t>Q11 | How likely are you to recommend the provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
         </is>
       </c>
       <c r="AA55" s="6" t="inlineStr">
         <is>
-          <t>Derived by rule from the questionnaire's own tables.</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
       <c r="AB55" s="10" t="inlineStr">
@@ -9431,12 +9432,12 @@
       </c>
       <c r="AD55" s="6" t="inlineStr">
         <is>
-          <t>It does not prove why the question was absent beyond the display rule; the check confirms the respondent was still travelling and had not been screened out. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE55" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality, rule_precedence</t>
+          <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
       </c>
     </row>
@@ -9446,7 +9447,7 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Q11</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
@@ -9471,17 +9472,17 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Q10 blocks a blank answer</t>
+          <t>Q11 blocks a blank answer</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>Prove Q10 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove Q11 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J56" s="6" t="inlineStr">
@@ -9496,7 +9497,7 @@
       </c>
       <c r="L56" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as Q10.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q11.</t>
         </is>
       </c>
       <c r="M56" s="6" t="inlineStr">
@@ -9506,8 +9507,8 @@
       </c>
       <c r="N56" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully
-then: At Q10, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor
+then: At Q11, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O56" s="6" t="inlineStr">
@@ -9517,32 +9518,32 @@
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q10 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q10 is the one the claim turns on.</t>
+          <t>Every answer before Q11 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q11 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
-          <t>At Q10, select nothing at all, then submit.</t>
+          <t>At Q11, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10  (refused at Q10; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11  (refused at Q11; respondent stays put)</t>
         </is>
       </c>
       <c r="S56" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11</t>
         </is>
       </c>
       <c r="T56" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q8, Q9, Q10</t>
         </is>
       </c>
       <c r="U56" s="6" t="inlineStr">
         <is>
-          <t>Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+          <t>Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V56" s="6" t="inlineStr">
@@ -9553,7 +9554,7 @@
       <c r="W56" s="6" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q10</t>
+2. an error message is shown against Q11</t>
         </is>
       </c>
       <c r="X56" s="6" t="inlineStr">
@@ -9568,12 +9569,12 @@
       </c>
       <c r="Z56" s="6" t="inlineStr">
         <is>
-          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
+          <t>Q11 | How likely are you to recommend the provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
         </is>
       </c>
       <c r="AA56" s="6" t="inlineStr">
         <is>
-          <t>Derived by rule from the questionnaire's own tables.</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
       <c r="AB56" s="10" t="inlineStr">
@@ -9603,7 +9604,7 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Q12</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
@@ -9618,7 +9619,7 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
@@ -9628,32 +9629,32 @@
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>Q10 quotes the answer given at Q9</t>
+          <t>Q12 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>Prove Q10's wording is built from the answer given at Q9, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove that answering Q12 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L57" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as Q10.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q12.</t>
         </is>
       </c>
       <c r="M57" s="6" t="inlineStr">
@@ -9663,8 +9664,8 @@
       </c>
       <c r="N57" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully
-then: At Q10, choose “Very poor”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O57" s="6" t="inlineStr">
@@ -9674,12 +9675,12 @@
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q10 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q10 is the one the claim turns on.</t>
+          <t>Every answer before Q12 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q12 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
-          <t>At Q10, choose “Very poor”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
@@ -9694,14 +9695,14 @@
       </c>
       <c r="T57" s="6" t="inlineStr">
         <is>
+          <t>Q8, Q9, Q10</t>
+        </is>
+      </c>
+      <c r="U57" s="6" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U57" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="V57" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
@@ -9709,7 +9710,8 @@
       </c>
       <c r="W57" s="6" t="inlineStr">
         <is>
-          <t>1. Q10's wording includes: Yes, fully</t>
+          <t>1. Q12 is on screen
+2. the next question shown is Q13</t>
         </is>
       </c>
       <c r="X57" s="6" t="inlineStr">
@@ -9724,7 +9726,7 @@
       </c>
       <c r="Z57" s="6" t="inlineStr">
         <is>
-          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
+          <t>Q12 | How likely are you to continue using the provider? | single | Definitely not; Probably not; Unsure; Probably; Definitely | Always show</t>
         </is>
       </c>
       <c r="AA57" s="6" t="inlineStr">
@@ -9744,7 +9746,7 @@
       </c>
       <c r="AD57" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE57" s="6" t="inlineStr">
@@ -9759,7 +9761,7 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Q12</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -9774,32 +9776,32 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>9. Rule Interaction</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>Q10 is shown and reflects its dependency on Q9 at the same time</t>
+          <t>Q12 blocks a blank answer</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>Prove Q10 is shown by its display rule and simultaneously reflects its dependency on Q9. Each mechanism can be correct alone and still disagree together.</t>
+          <t>Prove Q12 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>Individually correct rules can combine into behaviour neither one describes on its own.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
@@ -9809,7 +9811,7 @@
       </c>
       <c r="L58" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as Q10.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q12.</t>
         </is>
       </c>
       <c r="M58" s="6" t="inlineStr">
@@ -9819,59 +9821,59 @@
       </c>
       <c r="N58" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully
-then: At Q10, choose “Very poor”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0
+then: At Q12, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O58" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q10 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q10 is the one the claim turns on.</t>
+          <t>Every answer before Q12 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q12 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q58" s="6" t="inlineStr">
         <is>
-          <t>At Q10, choose “Very poor”, then submit.</t>
+          <t>At Q12, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12  (refused at Q12; respondent stays put)</t>
         </is>
       </c>
       <c r="S58" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12</t>
         </is>
       </c>
       <c r="T58" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q8, Q9, Q10</t>
         </is>
       </c>
       <c r="U58" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V58" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W58" s="6" t="inlineStr">
         <is>
-          <t>1. Q10 is on screen
-2. Q10's wording includes: Yes, fully</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q12</t>
         </is>
       </c>
       <c r="X58" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y58" s="6" t="inlineStr">
@@ -9881,7 +9883,7 @@
       </c>
       <c r="Z58" s="6" t="inlineStr">
         <is>
-          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
+          <t>Q12 | How likely are you to continue using the provider? | single | Definitely not; Probably not; Unsure; Probably; Definitely | Always show</t>
         </is>
       </c>
       <c r="AA58" s="6" t="inlineStr">
@@ -9901,7 +9903,7 @@
       </c>
       <c r="AD58" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE58" s="6" t="inlineStr">
@@ -9916,7 +9918,7 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>Q13</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -9946,12 +9948,12 @@
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>Q11 accepts a normal answer and the survey moves on</t>
+          <t>Q13 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q11 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove that answering Q13 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr">
@@ -9966,7 +9968,7 @@
       </c>
       <c r="L59" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q11.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q13.</t>
         </is>
       </c>
       <c r="M59" s="6" t="inlineStr">
@@ -9987,7 +9989,7 @@
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q11 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q11 is the one the claim turns on.</t>
+          <t>Every answer before Q13 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q13 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q59" s="6" t="inlineStr">
@@ -10022,8 +10024,8 @@
       </c>
       <c r="W59" s="6" t="inlineStr">
         <is>
-          <t>1. Q11 is on screen
-2. the next question shown is Q12</t>
+          <t>1. Q13 is on screen
+2. the next question shown is DT2</t>
         </is>
       </c>
       <c r="X59" s="6" t="inlineStr">
@@ -10038,7 +10040,7 @@
       </c>
       <c r="Z59" s="6" t="inlineStr">
         <is>
-          <t>Q11 | How likely are you to recommend the provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
+          <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
         </is>
       </c>
       <c r="AA59" s="6" t="inlineStr">
@@ -10073,7 +10075,7 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>Q13</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
@@ -10103,12 +10105,12 @@
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>Q11 blocks a blank answer</t>
+          <t>Q13 blocks a blank answer</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>Prove Q11 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove Q13 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J60" s="6" t="inlineStr">
@@ -10123,7 +10125,7 @@
       </c>
       <c r="L60" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q11.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q13.</t>
         </is>
       </c>
       <c r="M60" s="6" t="inlineStr">
@@ -10133,8 +10135,8 @@
       </c>
       <c r="N60" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor
-then: At Q11, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not
+then: At Q13, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O60" s="6" t="inlineStr">
@@ -10144,22 +10146,22 @@
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q11 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q11 is the one the claim turns on.</t>
+          <t>Every answer before Q13 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q13 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q60" s="6" t="inlineStr">
         <is>
-          <t>At Q11, select nothing at all, then submit.</t>
+          <t>At Q13, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11  (refused at Q11; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13  (refused at Q13; respondent stays put)</t>
         </is>
       </c>
       <c r="S60" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13</t>
         </is>
       </c>
       <c r="T60" s="6" t="inlineStr">
@@ -10169,7 +10171,7 @@
       </c>
       <c r="U60" s="6" t="inlineStr">
         <is>
-          <t>Q12, Q13, DT2, D1, D2, Q14</t>
+          <t>DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V60" s="6" t="inlineStr">
@@ -10180,7 +10182,7 @@
       <c r="W60" s="6" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q11</t>
+2. an error message is shown against Q13</t>
         </is>
       </c>
       <c r="X60" s="6" t="inlineStr">
@@ -10195,7 +10197,7 @@
       </c>
       <c r="Z60" s="6" t="inlineStr">
         <is>
-          <t>Q11 | How likely are you to recommend the provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
+          <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
         </is>
       </c>
       <c r="AA60" s="6" t="inlineStr">
@@ -10230,7 +10232,7 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>Q13</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -10245,12 +10247,12 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>4. Randomization</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8. Implementation Conformance</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
@@ -10260,17 +10262,17 @@
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Q11 quotes the answer given at Q1</t>
+          <t>Q13 shuffles without losing an option</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>Prove Q11's wording is built from the answer given at Q1, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove Q13 still presents all 5 of its options when shuffled, with none dropped and none repeated.</t>
         </is>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
+          <t>Without a genuine shuffle the option order biases the answers, and without the recorded order the answers cannot be corrected later.</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
@@ -10280,7 +10282,7 @@
       </c>
       <c r="L61" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q11.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q13.</t>
         </is>
       </c>
       <c r="M61" s="6" t="inlineStr">
@@ -10290,8 +10292,8 @@
       </c>
       <c r="N61" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor
-then: At Q11, choose “0”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not
+then: At Q13, choose “Lower cost”, then submit.</t>
         </is>
       </c>
       <c r="O61" s="6" t="inlineStr">
@@ -10301,12 +10303,12 @@
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q11 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q11 is the one the claim turns on.</t>
+          <t>Every answer before Q13 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q13 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q61" s="6" t="inlineStr">
         <is>
-          <t>At Q11, choose “0”, then submit.</t>
+          <t>At Q13, choose “Lower cost”, then submit.</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
@@ -10336,7 +10338,8 @@
       </c>
       <c r="W61" s="6" t="inlineStr">
         <is>
-          <t>1. Q11's wording includes: Provider A</t>
+          <t>1. Q13 shows exactly 5 options, none missing or repeated
+2. the options shown at Q13 are exactly: Better staff support, Clearer information, Faster service, Improved digital experience, Lower cost</t>
         </is>
       </c>
       <c r="X61" s="6" t="inlineStr">
@@ -10351,7 +10354,7 @@
       </c>
       <c r="Z61" s="6" t="inlineStr">
         <is>
-          <t>Q11 | How likely are you to recommend the provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
+          <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
         </is>
       </c>
       <c r="AA61" s="6" t="inlineStr">
@@ -10371,7 +10374,7 @@
       </c>
       <c r="AD61" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the order varies, only that nothing was lost or repeated. Order is a separate test needing several runs.</t>
         </is>
       </c>
       <c r="AE61" s="6" t="inlineStr">
@@ -10386,27 +10389,27 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Q12</t>
+          <t>Q13</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>TC-FT54</t>
+          <t>TC-ST03</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>FOCUSED</t>
+          <t>STATEFUL</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>4. Randomization</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8. Implementation Conformance</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
@@ -10416,27 +10419,27 @@
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>Q12 accepts a normal answer and the survey moves on</t>
+          <t>Q13 genuinely varies its option order</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q12 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q13 is genuinely shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on.</t>
         </is>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>Without a genuine shuffle the option order biases the answers, and without the recorded order the answers cannot be corrected later.</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q12.</t>
+          <t>Run this same path 5 times and compare the recorded option order between runs.</t>
         </is>
       </c>
       <c r="M62" s="6" t="inlineStr">
@@ -10446,8 +10449,8 @@
       </c>
       <c r="N62" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not
+then: At Q13, choose “Lower cost”, then submit.</t>
         </is>
       </c>
       <c r="O62" s="6" t="inlineStr">
@@ -10457,12 +10460,12 @@
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q12 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q12 is the one the claim turns on.</t>
+          <t>Every answer before Q13 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q13 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q62" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q13, choose “Lower cost”, then submit.</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
@@ -10492,8 +10495,7 @@
       </c>
       <c r="W62" s="6" t="inlineStr">
         <is>
-          <t>1. Q12 is on screen
-2. the next question shown is Q13</t>
+          <t>1. the option order at Q13 is NOT identical on every run</t>
         </is>
       </c>
       <c r="X62" s="6" t="inlineStr">
@@ -10508,7 +10510,7 @@
       </c>
       <c r="Z62" s="6" t="inlineStr">
         <is>
-          <t>Q12 | How likely are you to continue using the provider? | single | Definitely not; Probably not; Unsure; Probably; Definitely | Always show</t>
+          <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
         </is>
       </c>
       <c r="AA62" s="6" t="inlineStr">
@@ -10528,7 +10530,7 @@
       </c>
       <c r="AD62" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove any particular order is correct, only that the order is not fixed.</t>
         </is>
       </c>
       <c r="AE62" s="6" t="inlineStr">
@@ -10543,12 +10545,12 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Q12</t>
+          <t>DT2</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>TC-FT55</t>
+          <t>TC-FT54</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -10558,12 +10560,12 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
@@ -10573,27 +10575,27 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Q12 blocks a blank answer</t>
+          <t>DT2 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>Prove Q12 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove that answering DT2 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q12.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as DT2.</t>
         </is>
       </c>
       <c r="M63" s="6" t="inlineStr">
@@ -10603,33 +10605,33 @@
       </c>
       <c r="N63" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0
-then: At Q12, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O63" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q12 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q12 is the one the claim turns on.</t>
+          <t>Every answer before DT2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at DT2 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q63" s="6" t="inlineStr">
         <is>
-          <t>At Q12, select nothing at all, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12  (refused at Q12; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S63" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T63" s="6" t="inlineStr">
@@ -10639,23 +10641,22 @@
       </c>
       <c r="U63" s="6" t="inlineStr">
         <is>
-          <t>Q13, DT2, D1, D2, Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V63" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W63" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q12</t>
+          <t>1. the next question shown is D1</t>
         </is>
       </c>
       <c r="X63" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y63" s="6" t="inlineStr">
@@ -10665,7 +10666,7 @@
       </c>
       <c r="Z63" s="6" t="inlineStr">
         <is>
-          <t>Q12 | How likely are you to continue using the provider? | single | Definitely not; Probably not; Unsure; Probably; Definitely | Always show</t>
+          <t>DT2 | You're almost done! Thank you for your answers. Just a few last questions about you to finish up. | text display | — | Always show</t>
         </is>
       </c>
       <c r="AA63" s="6" t="inlineStr">
@@ -10685,7 +10686,7 @@
       </c>
       <c r="AD63" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE63" s="6" t="inlineStr">
@@ -10700,12 +10701,12 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Q12</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>TC-FT56</t>
+          <t>TC-FT55</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -10715,7 +10716,7 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -10730,27 +10731,27 @@
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>Q12 quotes the answer given at Q1</t>
+          <t>D1 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>Prove Q12's wording is built from the answer given at Q1, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove that answering D1 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K64" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L64" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q12.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as D1.</t>
         </is>
       </c>
       <c r="M64" s="6" t="inlineStr">
@@ -10760,8 +10761,8 @@
       </c>
       <c r="N64" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0
-then: At Q12, choose “Definitely not”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O64" s="6" t="inlineStr">
@@ -10771,12 +10772,12 @@
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q12 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q12 is the one the claim turns on.</t>
+          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q64" s="6" t="inlineStr">
         <is>
-          <t>At Q12, choose “Definitely not”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
@@ -10806,7 +10807,8 @@
       </c>
       <c r="W64" s="6" t="inlineStr">
         <is>
-          <t>1. Q12's wording includes: Provider A</t>
+          <t>1. D1 is on screen
+2. the next question shown is D2</t>
         </is>
       </c>
       <c r="X64" s="6" t="inlineStr">
@@ -10821,7 +10823,7 @@
       </c>
       <c r="Z64" s="6" t="inlineStr">
         <is>
-          <t>Q12 | How likely are you to continue using the provider? | single | Definitely not; Probably not; Unsure; Probably; Definitely | Always show</t>
+          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
       <c r="AA64" s="6" t="inlineStr">
@@ -10841,7 +10843,7 @@
       </c>
       <c r="AD64" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE64" s="6" t="inlineStr">
@@ -10856,12 +10858,12 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>TC-FT57</t>
+          <t>TC-FT56</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -10871,12 +10873,12 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
@@ -10886,27 +10888,27 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Q13 accepts a normal answer and the survey moves on</t>
+          <t>D1 blocks a blank answer</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q13 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove D1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q13.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as D1.</t>
         </is>
       </c>
       <c r="M65" s="6" t="inlineStr">
@@ -10916,33 +10918,33 @@
       </c>
       <c r="N65" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
+then: At D1, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O65" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q13 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q13 is the one the claim turns on.</t>
+          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q65" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At D1, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1  (refused at D1; respondent stays put)</t>
         </is>
       </c>
       <c r="S65" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1</t>
         </is>
       </c>
       <c r="T65" s="6" t="inlineStr">
@@ -10952,23 +10954,23 @@
       </c>
       <c r="U65" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>D2, Q14</t>
         </is>
       </c>
       <c r="V65" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W65" s="6" t="inlineStr">
         <is>
-          <t>1. Q13 is on screen
-2. the next question shown is DT2</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against D1</t>
         </is>
       </c>
       <c r="X65" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y65" s="6" t="inlineStr">
@@ -10978,7 +10980,7 @@
       </c>
       <c r="Z65" s="6" t="inlineStr">
         <is>
-          <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
+          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
       <c r="AA65" s="6" t="inlineStr">
@@ -10998,7 +11000,7 @@
       </c>
       <c r="AD65" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE65" s="6" t="inlineStr">
@@ -11013,12 +11015,12 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>TC-FT58</t>
+          <t>TC-FT57</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -11028,42 +11030,42 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>5. Quota / Stateful</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>6. Termination / Disposition</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>Q13 blocks a blank answer</t>
+          <t>QUOTA_REGION admits a respondent while D1-O1 is open</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>Prove Q13 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove QUOTA_REGION lets a 'North' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L66" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q13.</t>
+          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
         </is>
       </c>
       <c r="M66" s="6" t="inlineStr">
@@ -11073,59 +11075,58 @@
       </c>
       <c r="N66" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not
-then: At Q13, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
+then: At D1, choose “North”, then submit.</t>
         </is>
       </c>
       <c r="O66" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P66" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q13 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q13 is the one the claim turns on.</t>
+          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q66" s="6" t="inlineStr">
         <is>
-          <t>At Q13, select nothing at all, then submit.</t>
+          <t>At D1, choose “North”, then submit.</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13  (refused at Q13; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S66" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T66" s="6" t="inlineStr">
         <is>
-          <t>Q8, Q9, Q10</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U66" s="6" t="inlineStr">
         <is>
-          <t>DT2, D1, D2, Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V66" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W66" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q13</t>
+          <t>1. the respondent is allowed to continue</t>
         </is>
       </c>
       <c r="X66" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y66" s="6" t="inlineStr">
@@ -11135,7 +11136,7 @@
       </c>
       <c r="Z66" s="6" t="inlineStr">
         <is>
-          <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
+          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
       <c r="AA66" s="6" t="inlineStr">
@@ -11155,7 +11156,7 @@
       </c>
       <c r="AD66" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
         </is>
       </c>
       <c r="AE66" s="6" t="inlineStr">
@@ -11170,12 +11171,12 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>TC-FT59</t>
+          <t>TC-FT58</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -11185,42 +11186,42 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>4. Randomization</t>
+          <t>5. Quota / Stateful</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>8. Implementation Conformance</t>
+          <t>6. Termination / Disposition</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>Q13 shuffles without losing an option</t>
+          <t>QUOTA_REGION admits a respondent while D1-O2 is open</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>Prove Q13 still presents all 5 of its options when shuffled, with none dropped and none repeated.</t>
+          <t>Prove QUOTA_REGION lets a 'South' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>Without a genuine shuffle the option order biases the answers, and without the recorded order the answers cannot be corrected later.</t>
+          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q13.</t>
+          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
         </is>
       </c>
       <c r="M67" s="6" t="inlineStr">
@@ -11230,8 +11231,8 @@
       </c>
       <c r="N67" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not
-then: At Q13, choose “Lower cost”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
+then: At D1, choose “South”, then submit.</t>
         </is>
       </c>
       <c r="O67" s="6" t="inlineStr">
@@ -11241,12 +11242,12 @@
       </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q13 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q13 is the one the claim turns on.</t>
+          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q67" s="6" t="inlineStr">
         <is>
-          <t>At Q13, choose “Lower cost”, then submit.</t>
+          <t>At D1, choose “South”, then submit.</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
@@ -11261,7 +11262,7 @@
       </c>
       <c r="T67" s="6" t="inlineStr">
         <is>
-          <t>Q8, Q9, Q10</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U67" s="6" t="inlineStr">
@@ -11276,8 +11277,7 @@
       </c>
       <c r="W67" s="6" t="inlineStr">
         <is>
-          <t>1. Q13 shows exactly 5 options, none missing or repeated
-2. the options shown at Q13 are exactly: Better staff support, Clearer information, Faster service, Improved digital experience, Lower cost</t>
+          <t>1. the respondent is allowed to continue</t>
         </is>
       </c>
       <c r="X67" s="6" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="Z67" s="6" t="inlineStr">
         <is>
-          <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
+          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
       <c r="AA67" s="6" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="AD67" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the order varies, only that nothing was lost or repeated. Order is a separate test needing several runs.</t>
+          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
         </is>
       </c>
       <c r="AE67" s="6" t="inlineStr">
@@ -11327,57 +11327,57 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>TC-ST03</t>
+          <t>TC-FT59</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>STATEFUL</t>
+          <t>FOCUSED</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>4. Randomization</t>
+          <t>5. Quota / Stateful</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>8. Implementation Conformance</t>
+          <t>6. Termination / Disposition</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>Q13 genuinely varies its option order</t>
+          <t>QUOTA_REGION admits a respondent while D1-O3 is open</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>Prove Q13 is genuinely shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on.</t>
+          <t>Prove QUOTA_REGION lets a 'East' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>Without a genuine shuffle the option order biases the answers, and without the recorded order the answers cannot be corrected later.</t>
+          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr">
         <is>
-          <t>Run this same path 5 times and compare the recorded option order between runs.</t>
+          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
         </is>
       </c>
       <c r="M68" s="6" t="inlineStr">
@@ -11387,8 +11387,8 @@
       </c>
       <c r="N68" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not
-then: At Q13, choose “Lower cost”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
+then: At D1, choose “East”, then submit.</t>
         </is>
       </c>
       <c r="O68" s="6" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="P68" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q13 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q13 is the one the claim turns on.</t>
+          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q68" s="6" t="inlineStr">
         <is>
-          <t>At Q13, choose “Lower cost”, then submit.</t>
+          <t>At D1, choose “East”, then submit.</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="T68" s="6" t="inlineStr">
         <is>
-          <t>Q8, Q9, Q10</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U68" s="6" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="W68" s="6" t="inlineStr">
         <is>
-          <t>1. the option order at Q13 is NOT identical on every run</t>
+          <t>1. the respondent is allowed to continue</t>
         </is>
       </c>
       <c r="X68" s="6" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="Z68" s="6" t="inlineStr">
         <is>
-          <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
+          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
       <c r="AA68" s="6" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="AD68" s="6" t="inlineStr">
         <is>
-          <t>It does not prove any particular order is correct, only that the order is not fixed.</t>
+          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
         </is>
       </c>
       <c r="AE68" s="6" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>DT2</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
@@ -11498,42 +11498,42 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>5. Quota / Stateful</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6. Termination / Disposition</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>DT2 accepts a normal answer and the survey moves on</t>
+          <t>QUOTA_REGION admits a respondent while D1-O4 is open</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering DT2 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove QUOTA_REGION lets a 'West' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as DT2.</t>
+          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
         </is>
       </c>
       <c r="M69" s="6" t="inlineStr">
@@ -11543,8 +11543,8 @@
       </c>
       <c r="N69" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
+then: At D1, choose “West”, then submit.</t>
         </is>
       </c>
       <c r="O69" s="6" t="inlineStr">
@@ -11554,12 +11554,12 @@
       </c>
       <c r="P69" s="6" t="inlineStr">
         <is>
-          <t>Every answer before DT2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at DT2 is the one the claim turns on.</t>
+          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q69" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At D1, choose “West”, then submit.</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="T69" s="6" t="inlineStr">
         <is>
-          <t>Q8, Q9, Q10</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U69" s="6" t="inlineStr">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="W69" s="6" t="inlineStr">
         <is>
-          <t>1. the next question shown is D1</t>
+          <t>1. the respondent is allowed to continue</t>
         </is>
       </c>
       <c r="X69" s="6" t="inlineStr">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="Z69" s="6" t="inlineStr">
         <is>
-          <t>DT2 | You're almost done! Thank you for your answers. Just a few last questions about you to finish up. | text display | — | Always show</t>
+          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
       <c r="AA69" s="6" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="AD69" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
         </is>
       </c>
       <c r="AE69" s="6" t="inlineStr">
@@ -11654,42 +11654,42 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>5. Quota / Stateful</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6. Termination / Disposition</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>D1 accepts a normal answer and the survey moves on</t>
+          <t>QUOTA_REGION admits a respondent while D1-O5 is open</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering D1 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove QUOTA_REGION lets a 'Central' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as D1.</t>
+          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
         </is>
       </c>
       <c r="M70" s="6" t="inlineStr">
@@ -11699,8 +11699,8 @@
       </c>
       <c r="N70" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
+then: At D1, choose “Central”, then submit.</t>
         </is>
       </c>
       <c r="O70" s="6" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="Q70" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At D1, choose “Central”, then submit.</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="T70" s="6" t="inlineStr">
         <is>
-          <t>Q8, Q9, Q10</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U70" s="6" t="inlineStr">
@@ -11745,8 +11745,7 @@
       </c>
       <c r="W70" s="6" t="inlineStr">
         <is>
-          <t>1. D1 is on screen
-2. the next question shown is D2</t>
+          <t>1. the respondent is allowed to continue</t>
         </is>
       </c>
       <c r="X70" s="6" t="inlineStr">
@@ -11781,7 +11780,7 @@
       </c>
       <c r="AD70" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
         </is>
       </c>
       <c r="AE70" s="6" t="inlineStr">
@@ -11796,7 +11795,7 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
@@ -11811,12 +11810,12 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
@@ -11826,27 +11825,27 @@
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>D1 blocks a blank answer</t>
+          <t>D2 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>Prove D1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove that answering D2 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as D1.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as D2.</t>
         </is>
       </c>
       <c r="M71" s="6" t="inlineStr">
@@ -11856,33 +11855,33 @@
       </c>
       <c r="N71" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
-then: At D1, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O71" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P71" s="6" t="inlineStr">
         <is>
-          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
+          <t>Every answer before D2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D2 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q71" s="6" t="inlineStr">
         <is>
-          <t>At D1, select nothing at all, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1  (refused at D1; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S71" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T71" s="6" t="inlineStr">
@@ -11892,23 +11891,23 @@
       </c>
       <c r="U71" s="6" t="inlineStr">
         <is>
-          <t>D2, Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V71" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W71" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against D1</t>
+          <t>1. D2 is on screen
+2. the next question shown is Q14</t>
         </is>
       </c>
       <c r="X71" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y71" s="6" t="inlineStr">
@@ -11918,7 +11917,7 @@
       </c>
       <c r="Z71" s="6" t="inlineStr">
         <is>
-          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
+          <t>D2 | Which age group describes you? | single | 18-24; 25-34; 35-44; 45-54; 55+ | Always show</t>
         </is>
       </c>
       <c r="AA71" s="6" t="inlineStr">
@@ -11938,7 +11937,7 @@
       </c>
       <c r="AD71" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE71" s="6" t="inlineStr">
@@ -11953,7 +11952,7 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
@@ -11968,42 +11967,42 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>5. Quota / Stateful</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>6. Termination / Disposition</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_REGION admits a respondent while D1-O1 is open</t>
+          <t>D2 blocks a blank answer</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_REGION lets a 'North' respondent through while that group is below its target.</t>
+          <t>Prove D2 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L72" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as D2.</t>
         </is>
       </c>
       <c r="M72" s="6" t="inlineStr">
@@ -12013,58 +12012,59 @@
       </c>
       <c r="N72" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
-then: At D1, choose “North”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North
+then: At D2, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O72" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P72" s="6" t="inlineStr">
         <is>
-          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
+          <t>Every answer before D2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D2 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q72" s="6" t="inlineStr">
         <is>
-          <t>At D1, choose “North”, then submit.</t>
+          <t>At D2, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2  (refused at D2; respondent stays put)</t>
         </is>
       </c>
       <c r="S72" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2</t>
         </is>
       </c>
       <c r="T72" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q8, Q9, Q10</t>
         </is>
       </c>
       <c r="U72" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q14</t>
         </is>
       </c>
       <c r="V72" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W72" s="6" t="inlineStr">
         <is>
-          <t>1. the respondent is allowed to continue</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against D2</t>
         </is>
       </c>
       <c r="X72" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y72" s="6" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="Z72" s="6" t="inlineStr">
         <is>
-          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
+          <t>D2 | Which age group describes you? | single | 18-24; 25-34; 35-44; 45-54; 55+ | Always show</t>
         </is>
       </c>
       <c r="AA72" s="6" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="AD72" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE72" s="6" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>Q14</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
@@ -12124,42 +12124,42 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>5. Quota / Stateful</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>6. Termination / Disposition</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_REGION admits a respondent while D1-O2 is open</t>
+          <t>Q14 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_REGION lets a 'South' respondent through while that group is below its target.</t>
+          <t>Prove that answering Q14 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
         </is>
       </c>
       <c r="M73" s="6" t="inlineStr">
@@ -12169,8 +12169,8 @@
       </c>
       <c r="N73" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
-then: At D1, choose “South”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O73" s="6" t="inlineStr">
@@ -12180,12 +12180,12 @@
       </c>
       <c r="P73" s="6" t="inlineStr">
         <is>
-          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
+          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q73" s="6" t="inlineStr">
         <is>
-          <t>At D1, choose “South”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
@@ -12200,14 +12200,14 @@
       </c>
       <c r="T73" s="6" t="inlineStr">
         <is>
+          <t>Q8, Q9, Q10</t>
+        </is>
+      </c>
+      <c r="U73" s="6" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U73" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="V73" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
@@ -12215,7 +12215,8 @@
       </c>
       <c r="W73" s="6" t="inlineStr">
         <is>
-          <t>1. the respondent is allowed to continue</t>
+          <t>1. Q14 is on screen
+2. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
       <c r="X73" s="6" t="inlineStr">
@@ -12230,7 +12231,8 @@
       </c>
       <c r="Z73" s="6" t="inlineStr">
         <is>
-          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
+          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
+Optional</t>
         </is>
       </c>
       <c r="AA73" s="6" t="inlineStr">
@@ -12250,7 +12252,7 @@
       </c>
       <c r="AD73" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE73" s="6" t="inlineStr">
@@ -12265,7 +12267,7 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>Q14</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
@@ -12280,42 +12282,42 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>5. Quota / Stateful</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>6. Termination / Disposition</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_REGION admits a respondent while D1-O3 is open</t>
+          <t>Q14 accepts a valid answer</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_REGION lets a 'East' respondent through while that group is below its target.</t>
+          <t>Prove Q14 accepts an answer that obeys its stated rule. The rule is: at most 750 characters</t>
         </is>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
         </is>
       </c>
       <c r="M74" s="6" t="inlineStr">
@@ -12325,23 +12327,23 @@
       </c>
       <c r="N74" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
-then: At D1, choose “East”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: At Q14, type “x”, then submit.</t>
         </is>
       </c>
       <c r="O74" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>VALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P74" s="6" t="inlineStr">
         <is>
-          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
+          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q74" s="6" t="inlineStr">
         <is>
-          <t>At D1, choose “East”, then submit.</t>
+          <t>At Q14, type “x”, then submit.</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
@@ -12356,14 +12358,14 @@
       </c>
       <c r="T74" s="6" t="inlineStr">
         <is>
+          <t>Q8, Q9, Q10</t>
+        </is>
+      </c>
+      <c r="U74" s="6" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U74" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="V74" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
@@ -12371,7 +12373,7 @@
       </c>
       <c r="W74" s="6" t="inlineStr">
         <is>
-          <t>1. the respondent is allowed to continue</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X74" s="6" t="inlineStr">
@@ -12386,7 +12388,8 @@
       </c>
       <c r="Z74" s="6" t="inlineStr">
         <is>
-          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
+          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
+Optional</t>
         </is>
       </c>
       <c r="AA74" s="6" t="inlineStr">
@@ -12406,7 +12409,7 @@
       </c>
       <c r="AD74" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE74" s="6" t="inlineStr">
@@ -12421,7 +12424,7 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>Q14</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
@@ -12436,42 +12439,42 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>5. Quota / Stateful</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>6. Termination / Disposition</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_REGION admits a respondent while D1-O4 is open</t>
+          <t>Q14 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_REGION lets a 'West' respondent through while that group is below its target.</t>
+          <t>Prove Q14 refuses an answer that breaks its stated rule. The rule is: at most 750 characters</t>
         </is>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
         </is>
       </c>
       <c r="M75" s="6" t="inlineStr">
@@ -12481,28 +12484,28 @@
       </c>
       <c r="N75" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
-then: At D1, choose “West”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: At Q14, type a 751-character answer, then submit.</t>
         </is>
       </c>
       <c r="O75" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>INVALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P75" s="6" t="inlineStr">
         <is>
-          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
+          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q75" s="6" t="inlineStr">
         <is>
-          <t>At D1, choose “West”, then submit.</t>
+          <t>At Q14, type a 751-character answer, then submit.</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14  (refused at Q14; respondent stays put)</t>
         </is>
       </c>
       <c r="S75" s="6" t="inlineStr">
@@ -12512,27 +12515,28 @@
       </c>
       <c r="T75" s="6" t="inlineStr">
         <is>
+          <t>Q8, Q9, Q10</t>
+        </is>
+      </c>
+      <c r="U75" s="6" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U75" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="V75" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W75" s="6" t="inlineStr">
         <is>
-          <t>1. the respondent is allowed to continue</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q14</t>
         </is>
       </c>
       <c r="X75" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y75" s="6" t="inlineStr">
@@ -12542,7 +12546,8 @@
       </c>
       <c r="Z75" s="6" t="inlineStr">
         <is>
-          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
+          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
+Optional</t>
         </is>
       </c>
       <c r="AA75" s="6" t="inlineStr">
@@ -12562,7 +12567,7 @@
       </c>
       <c r="AD75" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE75" s="6" t="inlineStr">
@@ -12577,7 +12582,7 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>Q14</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
@@ -12592,42 +12597,42 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>5. Quota / Stateful</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>6. Termination / Disposition</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_REGION admits a respondent while D1-O5 is open</t>
+          <t>Q14 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_REGION lets a 'Central' respondent through while that group is below its target.</t>
+          <t>Prove Q14 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
         </is>
       </c>
       <c r="M76" s="6" t="inlineStr">
@@ -12637,23 +12642,23 @@
       </c>
       <c r="N76" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
-then: At D1, choose “Central”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: At Q14, type nothing, then submit.</t>
         </is>
       </c>
       <c r="O76" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P76" s="6" t="inlineStr">
         <is>
-          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
+          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q76" s="6" t="inlineStr">
         <is>
-          <t>At D1, choose “Central”, then submit.</t>
+          <t>At Q14, type nothing, then submit.</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr">
@@ -12668,14 +12673,14 @@
       </c>
       <c r="T76" s="6" t="inlineStr">
         <is>
+          <t>Q8, Q9, Q10</t>
+        </is>
+      </c>
+      <c r="U76" s="6" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U76" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="V76" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
@@ -12683,7 +12688,7 @@
       </c>
       <c r="W76" s="6" t="inlineStr">
         <is>
-          <t>1. the respondent is allowed to continue</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X76" s="6" t="inlineStr">
@@ -12698,7 +12703,8 @@
       </c>
       <c r="Z76" s="6" t="inlineStr">
         <is>
-          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
+          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
+Optional</t>
         </is>
       </c>
       <c r="AA76" s="6" t="inlineStr">
@@ -12718,7 +12724,7 @@
       </c>
       <c r="AD76" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE76" s="6" t="inlineStr">
@@ -12733,7 +12739,7 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>Q14</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -12748,7 +12754,7 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
@@ -12763,17 +12769,17 @@
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>D2 accepts a normal answer and the survey moves on</t>
+          <t>Q14 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering D2 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q14 refuses an answer that breaks its stated rule. The rule is: at most 750 characters</t>
         </is>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
@@ -12783,7 +12789,7 @@
       </c>
       <c r="L77" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as D2.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
         </is>
       </c>
       <c r="M77" s="6" t="inlineStr">
@@ -12794,7 +12800,7 @@
       <c r="N77" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+then: At Q14, type a 750-character answer, then submit.</t>
         </is>
       </c>
       <c r="O77" s="6" t="inlineStr">
@@ -12804,12 +12810,12 @@
       </c>
       <c r="P77" s="6" t="inlineStr">
         <is>
-          <t>Every answer before D2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D2 is the one the claim turns on.</t>
+          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q77" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q14, type a 750-character answer, then submit.</t>
         </is>
       </c>
       <c r="R77" s="6" t="inlineStr">
@@ -12839,8 +12845,7 @@
       </c>
       <c r="W77" s="6" t="inlineStr">
         <is>
-          <t>1. D2 is on screen
-2. the next question shown is Q14</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X77" s="6" t="inlineStr">
@@ -12855,7 +12860,8 @@
       </c>
       <c r="Z77" s="6" t="inlineStr">
         <is>
-          <t>D2 | Which age group describes you? | single | 18-24; 25-34; 35-44; 45-54; 55+ | Always show</t>
+          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
+Optional</t>
         </is>
       </c>
       <c r="AA77" s="6" t="inlineStr">
@@ -12875,7 +12881,7 @@
       </c>
       <c r="AD77" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE77" s="6" t="inlineStr">
@@ -12890,7 +12896,7 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>Q14</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
@@ -12910,7 +12916,7 @@
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
@@ -12920,27 +12926,27 @@
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>D2 blocks a blank answer</t>
+          <t>Q14 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
-          <t>Prove D2 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove Q14 refuses an answer that breaks its stated rule. The rule is: at most 750 characters</t>
         </is>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K78" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L78" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as D2.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
         </is>
       </c>
       <c r="M78" s="6" t="inlineStr">
@@ -12950,33 +12956,33 @@
       </c>
       <c r="N78" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North
-then: At D2, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: At Q14, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="O78" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P78" s="6" t="inlineStr">
         <is>
-          <t>Every answer before D2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D2 is the one the claim turns on.</t>
+          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q78" s="6" t="inlineStr">
         <is>
-          <t>At D2, select nothing at all, then submit.</t>
+          <t>At Q14, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="R78" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2  (refused at D2; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S78" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T78" s="6" t="inlineStr">
@@ -12986,23 +12992,22 @@
       </c>
       <c r="U78" s="6" t="inlineStr">
         <is>
-          <t>Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V78" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W78" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against D2</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X78" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y78" s="6" t="inlineStr">
@@ -13012,7 +13017,8 @@
       </c>
       <c r="Z78" s="6" t="inlineStr">
         <is>
-          <t>D2 | Which age group describes you? | single | 18-24; 25-34; 35-44; 45-54; 55+ | Always show</t>
+          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
+Optional</t>
         </is>
       </c>
       <c r="AA78" s="6" t="inlineStr">
@@ -13032,7 +13038,7 @@
       </c>
       <c r="AD78" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE78" s="6" t="inlineStr">
@@ -13062,7 +13068,7 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
@@ -13077,22 +13083,22 @@
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>Q14 accepts a normal answer and the survey moves on</t>
+          <t>Q14 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q14 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q14 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr">
@@ -13108,7 +13114,7 @@
       <c r="N79" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+then: At Q14, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="O79" s="6" t="inlineStr">
@@ -13123,7 +13129,7 @@
       </c>
       <c r="Q79" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q14, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="R79" s="6" t="inlineStr">
@@ -13153,8 +13159,7 @@
       </c>
       <c r="W79" s="6" t="inlineStr">
         <is>
-          <t>1. Q14 is on screen
-2. the respondent reaches the normal thank-you page</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X79" s="6" t="inlineStr">
@@ -13190,12 +13195,12 @@
       </c>
       <c r="AD79" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE79" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
+          <t>Leans on an unconfirmed reading: multi_equality, whitespace_is_an_answer</t>
         </is>
       </c>
     </row>
@@ -13205,27 +13210,27 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Q14</t>
+          <t>whole survey</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>TC-FT71</t>
+          <t>TC-RT03</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>FOCUSED</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>6. Termination / Disposition</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
@@ -13235,27 +13240,27 @@
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>Q14 accepts a valid answer</t>
+          <t>End-to-end journey: COMPLETE by way of routing</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>Prove Q14 accepts an answer that obeys its stated rule. The rule is: at most 750 characters</t>
+          <t>Prove that a respondent answering as listed is shown exactly this sequence of questions, in this order, and ends at COMPLETE by way of the routing, checked at ?. Condition: . They should then see: “Thank you. Your response has been recorded.”</t>
         </is>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>Screening someone out incorrectly loses a valid respondent and the money spent recruiting them. Failing to screen someone out puts the wrong person in the sample.</t>
         </is>
       </c>
       <c r="K80" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as the end.</t>
         </is>
       </c>
       <c r="M80" s="6" t="inlineStr">
@@ -13264,1035 +13269,92 @@
         </is>
       </c>
       <c r="N80" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: At Q14, type “x”, then submit.</t>
-        </is>
-      </c>
-      <c r="O80" s="6" t="inlineStr">
-        <is>
-          <t>VALID_BOUNDARY</t>
-        </is>
-      </c>
-      <c r="P80" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q80" s="6" t="inlineStr">
-        <is>
-          <t>At Q14, type “x”, then submit.</t>
-        </is>
-      </c>
-      <c r="R80" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
-        </is>
-      </c>
-      <c r="S80" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
-        </is>
-      </c>
-      <c r="T80" s="6" t="inlineStr">
-        <is>
-          <t>Q8, Q9, Q10</t>
-        </is>
-      </c>
-      <c r="U80" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V80" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W80" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
-        </is>
-      </c>
-      <c r="X80" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y80" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z80" s="6" t="inlineStr">
-        <is>
-          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA80" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB80" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC80" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD80" s="6" t="inlineStr">
-        <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
-        </is>
-      </c>
-      <c r="AE80" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="B81" s="9" t="inlineStr">
-        <is>
-          <t>Q14</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT72</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>10. Negative / Robustness</t>
-        </is>
-      </c>
-      <c r="G81" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>Q14 rejects an invalid answer</t>
-        </is>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q14 refuses an answer that breaks its stated rule. The rule is: at most 750 characters</t>
-        </is>
-      </c>
-      <c r="J81" s="6" t="inlineStr">
-        <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
-        </is>
-      </c>
-      <c r="K81" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L81" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
-        </is>
-      </c>
-      <c r="M81" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N81" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: At Q14, type a 751-character answer, then submit.</t>
-        </is>
-      </c>
-      <c r="O81" s="6" t="inlineStr">
-        <is>
-          <t>INVALID_BOUNDARY</t>
-        </is>
-      </c>
-      <c r="P81" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q81" s="6" t="inlineStr">
-        <is>
-          <t>At Q14, type a 751-character answer, then submit.</t>
-        </is>
-      </c>
-      <c r="R81" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14  (refused at Q14; respondent stays put)</t>
-        </is>
-      </c>
-      <c r="S81" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
-        </is>
-      </c>
-      <c r="T81" s="6" t="inlineStr">
-        <is>
-          <t>Q8, Q9, Q10</t>
-        </is>
-      </c>
-      <c r="U81" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V81" s="6" t="inlineStr">
-        <is>
-          <t>No forward navigation - the same question must reappear.</t>
-        </is>
-      </c>
-      <c r="W81" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q14</t>
-        </is>
-      </c>
-      <c r="X81" s="6" t="inlineStr">
-        <is>
-          <t>Not reached - the respondent cannot progress</t>
-        </is>
-      </c>
-      <c r="Y81" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z81" s="6" t="inlineStr">
-        <is>
-          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA81" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB81" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC81" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD81" s="6" t="inlineStr">
-        <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
-        </is>
-      </c>
-      <c r="AE81" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="4" t="n">
-        <v>78</v>
-      </c>
-      <c r="B82" s="9" t="inlineStr">
-        <is>
-          <t>Q14</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT73</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G82" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>Q14 allows a blank answer, being optional</t>
-        </is>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q14 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
-        </is>
-      </c>
-      <c r="J82" s="6" t="inlineStr">
-        <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
-        </is>
-      </c>
-      <c r="K82" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L82" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
-        </is>
-      </c>
-      <c r="M82" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N82" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: At Q14, type nothing, then submit.</t>
-        </is>
-      </c>
-      <c r="O82" s="6" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="P82" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q82" s="6" t="inlineStr">
-        <is>
-          <t>At Q14, type nothing, then submit.</t>
-        </is>
-      </c>
-      <c r="R82" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
-        </is>
-      </c>
-      <c r="S82" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
-        </is>
-      </c>
-      <c r="T82" s="6" t="inlineStr">
-        <is>
-          <t>Q8, Q9, Q10</t>
-        </is>
-      </c>
-      <c r="U82" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V82" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W82" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
-        </is>
-      </c>
-      <c r="X82" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y82" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z82" s="6" t="inlineStr">
-        <is>
-          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA82" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB82" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC82" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD82" s="6" t="inlineStr">
-        <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
-        </is>
-      </c>
-      <c r="AE82" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="B83" s="9" t="inlineStr">
-        <is>
-          <t>Q14</t>
-        </is>
-      </c>
-      <c r="C83" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT74</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H83" s="6" t="inlineStr">
-        <is>
-          <t>Q14 rejects an invalid answer</t>
-        </is>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q14 refuses an answer that breaks its stated rule. The rule is: at most 750 characters</t>
-        </is>
-      </c>
-      <c r="J83" s="6" t="inlineStr">
-        <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
-        </is>
-      </c>
-      <c r="K83" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L83" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
-        </is>
-      </c>
-      <c r="M83" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N83" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: At Q14, type a 750-character answer, then submit.</t>
-        </is>
-      </c>
-      <c r="O83" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P83" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q83" s="6" t="inlineStr">
-        <is>
-          <t>At Q14, type a 750-character answer, then submit.</t>
-        </is>
-      </c>
-      <c r="R83" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
-        </is>
-      </c>
-      <c r="S83" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
-        </is>
-      </c>
-      <c r="T83" s="6" t="inlineStr">
-        <is>
-          <t>Q8, Q9, Q10</t>
-        </is>
-      </c>
-      <c r="U83" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V83" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W83" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
-        </is>
-      </c>
-      <c r="X83" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y83" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z83" s="6" t="inlineStr">
-        <is>
-          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA83" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB83" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC83" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD83" s="6" t="inlineStr">
-        <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
-        </is>
-      </c>
-      <c r="AE83" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>Q14</t>
-        </is>
-      </c>
-      <c r="C84" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT75</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F84" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G84" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H84" s="6" t="inlineStr">
-        <is>
-          <t>Q14 rejects an invalid answer</t>
-        </is>
-      </c>
-      <c r="I84" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q14 refuses an answer that breaks its stated rule. The rule is: at most 750 characters</t>
-        </is>
-      </c>
-      <c r="J84" s="6" t="inlineStr">
-        <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
-        </is>
-      </c>
-      <c r="K84" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L84" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
-        </is>
-      </c>
-      <c r="M84" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N84" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: At Q14, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
-        </is>
-      </c>
-      <c r="O84" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P84" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q84" s="6" t="inlineStr">
-        <is>
-          <t>At Q14, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
-        </is>
-      </c>
-      <c r="R84" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
-        </is>
-      </c>
-      <c r="S84" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
-        </is>
-      </c>
-      <c r="T84" s="6" t="inlineStr">
-        <is>
-          <t>Q8, Q9, Q10</t>
-        </is>
-      </c>
-      <c r="U84" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V84" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W84" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
-        </is>
-      </c>
-      <c r="X84" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y84" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z84" s="6" t="inlineStr">
-        <is>
-          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA84" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB84" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC84" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD84" s="6" t="inlineStr">
-        <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
-        </is>
-      </c>
-      <c r="AE84" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t>Q14</t>
-        </is>
-      </c>
-      <c r="C85" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT76</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G85" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H85" s="6" t="inlineStr">
-        <is>
-          <t>Q14 allows a blank answer, being optional</t>
-        </is>
-      </c>
-      <c r="I85" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q14 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
-        </is>
-      </c>
-      <c r="J85" s="6" t="inlineStr">
-        <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
-        </is>
-      </c>
-      <c r="K85" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L85" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
-        </is>
-      </c>
-      <c r="M85" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N85" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: At Q14, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="O85" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P85" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q85" s="6" t="inlineStr">
-        <is>
-          <t>At Q14, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="R85" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
-        </is>
-      </c>
-      <c r="S85" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
-        </is>
-      </c>
-      <c r="T85" s="6" t="inlineStr">
-        <is>
-          <t>Q8, Q9, Q10</t>
-        </is>
-      </c>
-      <c r="U85" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V85" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W85" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
-        </is>
-      </c>
-      <c r="X85" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y85" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z85" s="6" t="inlineStr">
-        <is>
-          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA85" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB85" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC85" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD85" s="6" t="inlineStr">
-        <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
-        </is>
-      </c>
-      <c r="AE85" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: multi_equality, whitespace_is_an_answer</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="4" t="n">
-        <v>82</v>
-      </c>
-      <c r="B86" s="9" t="inlineStr">
-        <is>
-          <t>whole survey</t>
-        </is>
-      </c>
-      <c r="C86" s="7" t="inlineStr">
-        <is>
-          <t>TC-RT03</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>ROUTE</t>
-        </is>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>6. Termination / Disposition</t>
-        </is>
-      </c>
-      <c r="F86" s="6" t="inlineStr">
-        <is>
-          <t>1. Flow / Routing</t>
-        </is>
-      </c>
-      <c r="G86" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H86" s="6" t="inlineStr">
-        <is>
-          <t>End-to-end journey: COMPLETE by way of routing</t>
-        </is>
-      </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t>Prove that a respondent answering as listed is shown exactly this sequence of questions, in this order, and ends at COMPLETE by way of the routing, checked at ?. Condition: . They should then see: “Thank you. Your response has been recorded.”</t>
-        </is>
-      </c>
-      <c r="J86" s="6" t="inlineStr">
-        <is>
-          <t>Screening someone out incorrectly loses a valid respondent and the money spent recruiting them. Failing to screen someone out puts the wrong person in the sample.</t>
-        </is>
-      </c>
-      <c r="K86" s="6" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="L86" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as the end.</t>
-        </is>
-      </c>
-      <c r="M86" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N86" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Provider A; Q2 = Within 7 days; Q3 = Calls; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Dropped calls; Q8 = Dropped calls; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
 then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="O86" s="6" t="inlineStr">
+      <c r="O80" s="6" t="inlineStr">
         <is>
           <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
-      <c r="P86" s="6" t="inlineStr">
+      <c r="P80" s="6" t="inlineStr">
         <is>
           <t>Chosen to walk the whole survey without triggering a screen-out.</t>
         </is>
       </c>
-      <c r="Q86" s="6" t="inlineStr">
+      <c r="Q80" s="6" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="R86" s="6" t="inlineStr">
+      <c r="R80" s="6" t="inlineStr">
         <is>
           <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
-      <c r="S86" s="6" t="inlineStr">
+      <c r="S80" s="6" t="inlineStr">
         <is>
           <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
-      <c r="T86" s="6" t="inlineStr">
+      <c r="T80" s="6" t="inlineStr">
         <is>
           <t>Q8, Q9, Q10</t>
         </is>
       </c>
-      <c r="U86" s="6" t="inlineStr">
+      <c r="U80" s="6" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="V86" s="6" t="inlineStr">
+      <c r="V80" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
-      <c r="W86" s="6" t="inlineStr">
+      <c r="W80" s="6" t="inlineStr">
         <is>
           <t>1. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
-      <c r="X86" s="6" t="inlineStr">
+      <c r="X80" s="6" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="Y86" s="6" t="inlineStr">
+      <c r="Y80" s="6" t="inlineStr">
         <is>
           <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
         </is>
       </c>
-      <c r="Z86" s="6" t="inlineStr">
+      <c r="Z80" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AA86" s="6" t="inlineStr">
+      <c r="AA80" s="6" t="inlineStr">
         <is>
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB86" s="10" t="inlineStr">
+      <c r="AB80" s="10" t="inlineStr">
         <is>
           <t>PROVISIONAL</t>
         </is>
       </c>
-      <c r="AC86" s="8" t="inlineStr">
+      <c r="AC80" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AD86" s="6" t="inlineStr">
+      <c r="AD80" s="6" t="inlineStr">
         <is>
           <t>It does not prove any validation rule: every answer on this path is deliberately valid. It does not prove randomization or quota behaviour.</t>
         </is>
       </c>
-      <c r="AE86" s="6" t="inlineStr">
+      <c r="AE80" s="6" t="inlineStr">
         <is>
           <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
